--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF202"/>
+  <dimension ref="A1:AF204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>実来（みらい）</t>
+          <t>実来(みらい)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>実来（みらい）</t>
+          <t>実来(みらい)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>実来（みらい）の最新の口コミ</t>
+          <t>実来(みらい)の最新の口コミ</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>実来（みらい）の評判・口コミ</t>
+          <t>実来(みらい)の評判・口コミ</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
@@ -30005,132 +30005,132 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>company-428</t>
+          <t>company-31354</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>さいたま市不用品回収センター</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/saitamashi-fuyouhin/</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/saitamashi-fuyouhin.png</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>さいたま市不用品回収センター</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>4.87 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>さいたま市不用品回収センターは、地域最安級の価格設定で不用品回収を提供しているサービスです。豊富な実績を活かし、小さな不用品1点から家まるごとの大量処分まで柔軟に対応します。明朗会計で追加請求なしの明確な料金体系で安心して依頼でき、年中無休で早朝〜深夜の対応も可能です。 また、環境配慮の適正処理やリユース可能品の買取にも力を入れています。専任スタッフが一貫して対応し、迅速な対応と安心感が魅力です。</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>不用品整理：要見積もり</t>
+          <t>ミニパック：6,600円～ / ライトパック：13,200円～ / スタンダード：19,800円～ / ファミリー：39,600円～ / ビッグパック：66,000円～ / オーダーメイド：お見積り</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>未来応援隊の最新の口コミ</t>
+          <t>さいたま市不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>20歳・男性</t>
+          <t>20代・女性</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
+          <t>一人暮らしの引越しで不用品が一気に出てしまい、初めて業者さんに依頼しました。電話対応がとても丁寧で、料金や流れを分かりやすく説明してもらえたので不安なくお願いできました。当日はスタッフさんがテキパキ作業してくれて、重い家具もあっという間に搬出。部屋を傷つけないよう配慮してくれた点も好印象でした。忙しい引越し時に本当に助かりました。</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/saitamashi-fuyouhin/</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/saitamashi-fuyouhin.png</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>未来応援隊の評判・口コミ</t>
+          <t>さいたま市不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
@@ -30140,17 +30140,26 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
+          <t>年中無休で依頼可能 / 買取制度あり / 明朗会計で安心</t>
         </is>
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>さいたま市不用品回収センターは、地域最安級の価格設定で不用品回収を提供しているサービスです。豊富な実績を活かし、小さな不用品1点から家まるごとの大量処分まで柔軟に対応します。明朗会計で追加請求なしの明確な料金体系で安心して依頼でき、年中無休で早朝〜深夜の対応も可能です。 また、環境配慮の適正処理やリユース可能品の買取にも力を入れています。専任スタッフが一貫して対応し、迅速な対応と安心感が魅力です。</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>https://www.miraiouentai.com/</t>
+          <t>https://sakado-yousan.com/＂&gt;https://sakado-yousan.com/&lt;/a&gt;&lt;/td&gt;
+            &lt;/tr&gt;
+			     &lt;tr&gt;
+            &lt;th&gt;GoogleMap&lt;/th&gt;
+              &lt;td&gt;&lt;/td&gt;
+            &lt;/tr&gt;
+          &lt;/tbody&gt;
+        &lt;/table&gt;
+      &lt;/section&gt;
+      &lt;section id=</t>
         </is>
       </c>
     </row>
@@ -30163,37 +30172,37 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>company-632</t>
+          <t>company-31364</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>豊島区不用品回収センター</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/toshimaku-fuyouhin/</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/toshimaku-fuyouhin.png</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>豊島区不用品回収センター</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>4.75 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -30203,77 +30212,73 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>豊島区不用品回収センターは、豊島区全域（池袋・巣鴨・大塚・目白・駒込など）で不用品回収・片付けを行う地域密着型業者です。最短20分での対応が可能で、無料見積もり・明朗な料金提示を徹底しており、軽トラック積載で9,800円〜と分かりやすい価格体系です。また、一般家庭から法人・店舗の廃棄物、遺品整理・ゴミ屋敷清掃まで幅広く対応し、豊島区内で18年以上の実績と3,000件以上の取扱件数を誇ります。防護用マットや養生シートの使用で建物への配慮も徹底しています。</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>東京都 / 神奈川県</t>
-        </is>
-      </c>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
         <is>
-          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
+          <t>ライトプラン：4,900円～ / 軽車両まるごとプラン：9,900円～ / 中型車両プラン：19,900円～ / 大容量車両プラン：50,000円～ / 大型車両プラン：100,000円～ / カスタム対応プラン：個別見積もり</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの最新の口コミ</t>
+          <t>豊島区不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>70代・女性</t>
+          <t>30代・男性</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4.5・回収速度4.5・対応5）</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
+          <t>引越し前の片付けで不用品が一気に出てしまい依頼しました。問い合わせから見積もりまでが早く、回収日もこちらの希望に合わせてもらえたのが助かりました。当日はスタッフの方がテキパキ作業してくれて、大型家具も短時間で搬出。料金説明も分かりやすく、追加費用がなかった点も安心できました。忙しい時期でも頼みやすい業者だと思います。</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/toshimaku-fuyouhin/</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/toshimaku-fuyouhin.png</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの評判・口コミ</t>
+          <t>豊島区不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
@@ -30283,12 +30288,12 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
@@ -30298,17 +30303,17 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
+          <t>豊島区なら最短20分 / 買取制度あり / 18年の実績あり</t>
         </is>
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>豊島区不用品回収センターは、豊島区全域（池袋・巣鴨・大塚・目白・駒込など）で不用品回収・片付けを行う地域密着型業者です。最短20分での対応が可能で、無料見積もり・明朗な料金提示を徹底しており、軽トラック積載で9,800円〜と分かりやすい価格体系です。また、一般家庭から法人・店舗の廃棄物、遺品整理・ゴミ屋敷清掃まで幅広く対応し、豊島区内で18年以上の実績と3,000件以上の取扱件数を誇ります。防護用マットや養生シートの使用で建物への配慮も徹底しています。</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>https://www.freshman-s.com/</t>
+          <t>https://www.toshima-sjc.org/</t>
         </is>
       </c>
     </row>
@@ -30321,27 +30326,27 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>company-2133</t>
+          <t>company-428</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -30351,42 +30356,42 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>4.57 （ 7 件 ）</t>
+          <t>4.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
+          <t>不用品整理：要見積もり</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>片付け侍の最新の口コミ</t>
+          <t>未来応援隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>29歳・男性</t>
+          <t>20歳・男性</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -30396,12 +30401,12 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応3.5）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
+          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -30411,17 +30416,17 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>片付け侍の評判・口コミ</t>
+          <t>未来応援隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
@@ -30431,42 +30436,42 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
         </is>
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>https://katazuke-s.com/</t>
+          <t>https://www.miraiouentai.com/</t>
         </is>
       </c>
     </row>
@@ -30479,87 +30484,87 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>company-4087</t>
+          <t>company-632</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>3.91 （ 6 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>東京都 / 神奈川県</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>ECO助っ人の最新の口コミ</t>
+          <t>フレッシュマンサービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>57歳・女性</t>
+          <t>70代・女性</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度3.5・対応3）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -30569,62 +30574,62 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>ECO助っ人の評判・口コミ</t>
+          <t>フレッシュマンサービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
         </is>
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>https://eco-suketto.jp/</t>
+          <t>https://www.freshman-s.com/</t>
         </is>
       </c>
     </row>
@@ -30637,152 +30642,152 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>company-380</t>
+          <t>company-2133</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>3.87 （ 4 件 ）</t>
+          <t>4.57 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の最新の口コミ</t>
+          <t>片付け侍の最新の口コミ</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>63歳・女性</t>
+          <t>29歳・男性</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応3.5）</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の評判・口コミ</t>
+          <t>片付け侍の評判・口コミ</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
         </is>
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>https://koyorecycle.com/</t>
+          <t>https://katazuke-s.com/</t>
         </is>
       </c>
     </row>
@@ -30795,122 +30800,122 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>company-6234</t>
+          <t>company-4087</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>4.42 （ 7 件 ）</t>
+          <t>3.91 （ 6 件 ）</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの最新の口コミ</t>
+          <t>ECO助っ人の最新の口コミ</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>40代 男性</t>
+          <t>57歳・女性</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度3.5・対応3）</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの評判・口コミ</t>
+          <t>ECO助っ人の評判・口コミ</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -30920,27 +30925,27 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
         </is>
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
         <is>
-          <t>https://otasuke-master.co.jp/</t>
+          <t>https://eco-suketto.jp/</t>
         </is>
       </c>
     </row>
@@ -30953,72 +30958,72 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>company-8102</t>
+          <t>company-380</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>3.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>片付け堂の最新の口コミ</t>
+          <t>紅葉リサイクル福岡の最新の口コミ</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>63歳・女性</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -31028,12 +31033,12 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -31043,62 +31048,62 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>片付け堂の評判・口コミ</t>
+          <t>紅葉リサイクル福岡の評判・口コミ</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
         </is>
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>https://www.katazukedou.com/</t>
+          <t>https://koyorecycle.com/</t>
         </is>
       </c>
     </row>
@@ -31111,72 +31116,72 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>company-3871</t>
+          <t>company-6234</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>5 （ 3 件 ）</t>
+          <t>4.42 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>福島片付け110番の最新の口コミ</t>
+          <t>便利屋お助けマスターの最新の口コミ</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>40代・男性</t>
+          <t>40代 男性</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -31186,12 +31191,12 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -31201,62 +31206,62 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>福島片付け110番の評判・口コミ</t>
+          <t>便利屋お助けマスターの評判・口コミ</t>
         </is>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
         </is>
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>https://fukushima-kataduke110ban.com/</t>
+          <t>https://otasuke-master.co.jp/</t>
         </is>
       </c>
     </row>
@@ -31269,152 +31274,152 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>company-3850</t>
+          <t>company-8102</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>5 （ 2 件 ）</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>片付け堂の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>片付け堂の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>4.5 （ 4 件 ）</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>福島県 / 茨城県</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>フロンティアグループの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>30歳・男性</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度4・対応4）</t>
-        </is>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
-        </is>
-      </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>フロンティアグループの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
         </is>
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>https://iwaki-benriya.com/</t>
+          <t>https://www.katazukedou.com/</t>
         </is>
       </c>
     </row>
@@ -31427,72 +31432,72 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>company-615</t>
+          <t>company-3871</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>4.75 （ 4 件 ）</t>
+          <t>5 （ 3 件 ）</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>エコスピードの最新の口コミ</t>
+          <t>福島片付け110番の最新の口コミ</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>30代 女性</t>
+          <t>40代・男性</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -31502,77 +31507,77 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>エコスピードの評判・口コミ</t>
+          <t>福島片付け110番の評判・口コミ</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
         </is>
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
         <is>
-          <t>https://eco-speed.life/</t>
+          <t>https://fukushima-kataduke110ban.com/</t>
         </is>
       </c>
     </row>
@@ -31585,152 +31590,152 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>company-3839</t>
+          <t>company-3850</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フロンティアグループ</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フロンティアグループ</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>4.5 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>福島県 / 茨城県</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の最新の口コミ</t>
+          <t>フロンティアグループの最新の口コミ</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>30歳・男性</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度4・対応4）</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の評判・口コミ</t>
+          <t>フロンティアグループの評判・口コミ</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
         </is>
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+          <t>https://iwaki-benriya.com/</t>
         </is>
       </c>
     </row>
@@ -31743,150 +31748,466 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
+          <t>company-615</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>4.75 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>エコスピードの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>30代 女性</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>エコスピードの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>https://eco-speed.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>14</v>
+      </c>
+      <c r="B203" t="n">
+        <v>7</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>company-3839</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>5 （ 1 件 ）</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>14</v>
+      </c>
+      <c r="B204" t="n">
+        <v>8</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
           <t>company-418</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
         <is>
           <t>5 （ 2 件 ）</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
+      <c r="J204" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K204" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t>深夜・早朝の回収 / 即日対応 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t>福岡県 / 長崎県</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr">
+      <c r="N204" t="inlineStr">
         <is>
           <t>単品回収：1点1,000円より</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr">
+      <c r="O204" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の最新の口コミ</t>
         </is>
       </c>
-      <c r="P202" t="inlineStr">
+      <c r="P204" t="inlineStr">
         <is>
           <t>59歳・女性</t>
         </is>
       </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr">
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
         <is>
           <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
-      <c r="S202" t="inlineStr">
+      <c r="S204" t="inlineStr">
         <is>
           <t>問い合わせの迅速な対応。当日も親切に対応していただきました。また機会があれば利用したいと思います。ありがとうございました。</t>
         </is>
       </c>
-      <c r="T202" t="inlineStr">
+      <c r="T204" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="U204" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
+      <c r="V204" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="W202" t="inlineStr">
+      <c r="W204" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の評判・口コミ</t>
         </is>
       </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
         <is>
           <t>2件</t>
         </is>
       </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
         <is>
           <t>1点から不用品を回収してもらえる / 引越しとセットで依頼するとお得 / LINEでスピード見積もりに対応</t>
         </is>
       </c>
-      <c r="AE202" t="inlineStr">
+      <c r="AE204" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="AF202" t="inlineStr"/>
+      <c r="AF204" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF204"/>
+  <dimension ref="A1:AF213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30326,87 +30326,87 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>company-428</t>
+          <t>company-31398</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>沖縄不用品回収サービス</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/okinawa-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/okinawa-fuyouhin.png</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>沖縄不用品回収サービス</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>4.87 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>沖縄不用品回収サービスは、沖縄県内全域で不用品回収・粗大ごみ処理を行う地域密着型業者です。那覇市や浦添市、宜野湾市など主要都市から離島まで対応し、不用品1点から住宅・店舗まるごとの大量回収まで柔軟に対応しています。無料出張見積もり・明朗な料金体系を採用し、家電リサイクル法対象品や大型家具も回収可能です。また、買取サービスや遺品整理、ゴミ屋敷清掃、特殊清掃などもワンストップで提供しています。高いリサイクル率や迅速対応も強みです。</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>不用品整理：要見積もり</t>
+          <t>SSパック：4,800円～ / Sパック：9,800円～ / Mパック：19,800円～ / Lパック：42,800円～ / LLパック：85,800円～ / その他：別途お見積り</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>未来応援隊の最新の口コミ</t>
+          <t>沖縄不用品回収サービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>20歳・男性</t>
+          <t>40代・男性</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
+          <t>仕事が忙しく、部屋の片付けを後回しにしていたところ不用品が溜まってしまい依頼しました。問い合わせから見積もりまでがスムーズで、こちらの都合に合わせて回収日を調整してもらえたのが助かりました。当日はスタッフの方が手際よく作業してくれて、短時間で部屋が見違えるほどきれいに。自分で分別や運び出しをする必要がなく、想像以上に楽でした。</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -30416,44 +30416,44 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/okinawa-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/okinawa-fuyouhin.png</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>未来応援隊の評判・口コミ</t>
+          <t>沖縄不用品回収サービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
           <t>4.75</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
       <c r="AC193" t="inlineStr">
         <is>
           <t>5</t>
@@ -30461,17 +30461,17 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
+          <t>沖縄県内全域対応 / 買取サービス有 / 見積もり無料</t>
         </is>
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>沖縄不用品回収サービスは、沖縄県内全域で不用品回収・粗大ごみ処理を行う地域密着型業者です。那覇市や浦添市、宜野湾市など主要都市から離島まで対応し、不用品1点から住宅・店舗まるごとの大量回収まで柔軟に対応しています。無料出張見積もり・明朗な料金体系を採用し、家電リサイクル法対象品や大型家具も回収可能です。また、買取サービスや遺品整理、ゴミ屋敷清掃、特殊清掃などもワンストップで提供しています。高いリサイクル率や迅速対応も強みです。</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>https://www.miraiouentai.com/</t>
+          <t>https://hapi-toku.okinawa/</t>
         </is>
       </c>
     </row>
@@ -30484,27 +30484,27 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>company-632</t>
+          <t>company-31412</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>大田区不用品回収センター</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/otaku-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/otaku-fuyouhin.png</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>大田区不用品回収センター</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -30524,32 +30524,28 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>大田区不用品回収センターは、大田区全域に対応する地域密着型の不用品回収業者で、1点から大量処分まで柔軟に対応しています。最短即日対応・分別不要の回収体制が特徴で、現地で正確な無料見積もりを提示し明朗会計を徹底しています。定額パックプラン（カゴ台車・軽トラ・1.5t〜4t車）を用意し、引越しや遺品整理、ゴミ屋敷の片付け、オフィス・店舗の大量回収まで幅広く対応可能です。スタッフは清潔感と技術を備えた自社社員で、近隣配慮や養生もしっかり行い、環境面の適正処理にも取り組んでいます。</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>東京都 / 神奈川県</t>
-        </is>
-      </c>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
-          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
+          <t>カゴ台車パック：5,500円～ / 軽トラパック：12,000円～ / 1.5t車パック：25,000円～ / 2t車パック：45,000円～ / 4t車パック：80,000円～ / 法人プラン：要お見積り</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの最新の口コミ</t>
+          <t>大田区不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>70代・女性</t>
+          <t>40代・女性</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -30564,7 +30560,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
+          <t>マンションの片付けで利用しました。共用廊下やエレベーターの養生をしっかり行ってくれ、管理規約への配慮が感じられたのが好印象です。事前の説明も分かりやすく、回収当日もスムーズに作業が進みました。重たい家具や家電を自分で運ぶ必要がなく、短時間で部屋がすっきり。近隣への配慮も徹底しており、安心してお願いできる業者だと思います。</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -30574,17 +30570,17 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/otaku-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/otaku-fuyouhin.png</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの評判・口コミ</t>
+          <t>大田区不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
@@ -30614,22 +30610,22 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
+          <t>大田区内なら最短30分でお伺い / 現地見積もり無料 / 買取制度ありで明朗会計</t>
         </is>
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>大田区不用品回収センターは、大田区全域に対応する地域密着型の不用品回収業者で、1点から大量処分まで柔軟に対応しています。最短即日対応・分別不要の回収体制が特徴で、現地で正確な無料見積もりを提示し明朗会計を徹底しています。定額パックプラン（カゴ台車・軽トラ・1.5t〜4t車）を用意し、引越しや遺品整理、ゴミ屋敷の片付け、オフィス・店舗の大量回収まで幅広く対応可能です。スタッフは清潔感と技術を備えた自社社員で、近隣配慮や養生もしっかり行い、環境面の適正処理にも取り組んでいます。</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>https://www.freshman-s.com/</t>
+          <t>https://fc-sme-matching.jp/</t>
         </is>
       </c>
     </row>
@@ -30642,27 +30638,27 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>company-2133</t>
+          <t>company-31431</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>川口市不用品回収センター</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/kawaguchishi-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/kawaguchishi-fuyouhin.png</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>川口市不用品回収センター</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -30672,42 +30668,38 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>4.57 （ 7 件 ）</t>
+          <t>4.75 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>川口市不用品回収センターは、川口市全域を対象に即日・スピード対応が可能な地域密着型の不用品回収業者です。最短30分で到着する迅速サービスや、無料の現地見積もりと明朗会計が大きな強みです。家庭の不用品回収だけでなく、遺品整理・生前整理、ゴミ屋敷清掃、オフィス・店舗片付けまで幅広く対応しており、有資格者在籍の丁寧な対応も安心感につながっています。追加料金なしの定額パックや買取対応により、費用面でも利用者の負担を抑えられる仕組みが整っています。</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
-        </is>
-      </c>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
-          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
+          <t>SSパック：6,800円～ / Sパック：14,000円～ / Mパック：22,000円～ / Lパック：42,000円～ / XLパック：70,000円～ / カスタムプラン：別途お見積り</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>片付け侍の最新の口コミ</t>
+          <t>川口市不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>29歳・男性</t>
+          <t>30代・男性</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -30717,12 +30709,12 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応3.5）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
+          <t>部屋の整理を進める中で、不用品の処分方法を調べるのが面倒になり依頼しました。回収と買取をまとめて相談できたため、どれを処分すべきか判断しやすかったのが良かった点です。作業当日も淡々と進めてくれ、余計なやり取りがなくスムーズでした。費用はかかりますが、時間と手間を考えると納得できるサービスだと感じました。</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -30732,17 +30724,17 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/kawaguchishi-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/kawaguchishi-fuyouhin.png</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>片付け侍の評判・口コミ</t>
+          <t>川口市不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
@@ -30752,42 +30744,42 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+          <t>川口市なら最短30分で到着 / 買取制度あり / 有資格者在籍で安心</t>
         </is>
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>川口市不用品回収センターは、川口市全域を対象に即日・スピード対応が可能な地域密着型の不用品回収業者です。最短30分で到着する迅速サービスや、無料の現地見積もりと明朗会計が大きな強みです。家庭の不用品回収だけでなく、遺品整理・生前整理、ゴミ屋敷清掃、オフィス・店舗片付けまで幅広く対応しており、有資格者在籍の丁寧な対応も安心感につながっています。追加料金なしの定額パックや買取対応により、費用面でも利用者の負担を抑えられる仕組みが整っています。</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>https://katazuke-s.com/</t>
+          <t>https://www.press-osi.com/</t>
         </is>
       </c>
     </row>
@@ -30800,122 +30792,118 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>company-4087</t>
+          <t>company-31443</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>練馬区不用品回収センター</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/nerimaku-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/nerimaku-fuyouhin.png</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>練馬区不用品回収センター</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>3.91 （ 6 件 ）</t>
+          <t>4.5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>練馬区不用品回収センターは、区内全域をカバーする地域密着型サービスで、電話から最短30分で現場に駆けつける即日対応力が大きな強みです。明朗会計で出張見積もりが無料、追加料金なしの料金体系を徹底しており、初めての方でも安心して依頼できます。回収・買取は家具・家電のほか、清掃や片付けといった作業まで一括で任せることができ、再利用可能品の高価買取で費用を抑えられる可能性もあります。法令に基づく許可取得や24時間365日の受付体制も整っており、急な回収ニーズにも対応できる業者です。</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
-        </is>
-      </c>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
-          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+          <t>カゴ車プラン：4,900円～ / 軽トラックプラン：9,900円～ / 1.5tトラックプラン：14,800円～ / 2tトラックプラン：19,800円～ / 2t箱車プラン：29,800円～ / 大容量プラン：要見積</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>ECO助っ人の最新の口コミ</t>
+          <t>練馬区不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>57歳・女性</t>
+          <t>40代・男性</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度3.5・対応3）</t>
+          <t>（回収料金4.5・回収速度4.5・対応5）</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+          <t>実家の遺品整理で利用しました。何を残し、何を処分するか迷う場面もありましたが、作業を急かされることなく確認しながら進めてもらえたのが印象的です。事前説明も簡潔で分かりやすく、費用面も納得したうえで依頼できました。重たい家具や家電の搬出をすべて任せられ、精神的にも体力的にも負担が少なく助かりました。</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/nerimaku-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/nerimaku-fuyouhin.png</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>ECO助っ人の評判・口コミ</t>
+          <t>練馬区不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -30925,27 +30913,27 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+          <t>高価買取実績あり / 練馬区なら最短30分でお伺い / 清掃や片付けも追加対応可能</t>
         </is>
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>練馬区不用品回収センターは、区内全域をカバーする地域密着型サービスで、電話から最短30分で現場に駆けつける即日対応力が大きな強みです。明朗会計で出張見積もりが無料、追加料金なしの料金体系を徹底しており、初めての方でも安心して依頼できます。回収・買取は家具・家電のほか、清掃や片付けといった作業まで一括で任せることができ、再利用可能品の高価買取で費用を抑えられる可能性もあります。法令に基づく許可取得や24時間365日の受付体制も整っており、急な回収ニーズにも対応できる業者です。</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
         <is>
-          <t>https://eco-suketto.jp/</t>
+          <t>https://www.aka-shirt.com/</t>
         </is>
       </c>
     </row>
@@ -30958,72 +30946,68 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>company-380</t>
+          <t>company-31465</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>板橋区不用品回収センター</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/itabashiku-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/itabashiku-fuyouhin.png</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>板橋区不用品回収センター</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3.87 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>板橋区不用品回収センターは、板橋区全域対応の地域密着型不用品回収サービスで、最短30分での出張見積もり・即日対応が可能です。明確な料金体系で、見積もり時に提示した金額以外の追加費用がかからないのが特徴です。小物から大型家具・家電まで少量〜大量回収まで柔軟に対応し、経験豊富なスタッフが丁寧に搬出作業を行います。不要品の中に価値ある品があれば、その場で査定して買取対応も可能なため、処分費用の節約につながる場合もあります。</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
-          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+          <t>カゴ車プラン：4,900円～ / 軽トラック積み放題プラン：9,900円～ / 1.5tトラックプラン：14,800円～ / 2tトラックプラン：19,800円～ / 4tトラックプラン：29,800円～ / 大容量特別プラン：要見積</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の最新の口コミ</t>
+          <t>板橋区不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>63歳・女性</t>
+          <t>30代・女性</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -31033,12 +31017,12 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+          <t>引っ越し前の片付けで不用品が一気に出てしまい利用しました。限られたスケジュールの中でも日程調整がしやすく、見積もりから回収までスムーズだったのが印象的です。重たい家具や家電もまとめて回収してもらえたので、自分で粗大ゴミを手配する手間が省けました。引っ越し作業に集中できたので、本当に助かりました。</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -31048,62 +31032,62 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/itabashiku-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/itabashiku-fuyouhin.png</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の評判・口コミ</t>
+          <t>板橋区不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+          <t>買取対応も可能 / 板橋区内最短30分でお伺い / 追加費用一切なし</t>
         </is>
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>板橋区不用品回収センターは、板橋区全域対応の地域密着型不用品回収サービスで、最短30分での出張見積もり・即日対応が可能です。明確な料金体系で、見積もり時に提示した金額以外の追加費用がかからないのが特徴です。小物から大型家具・家電まで少量〜大量回収まで柔軟に対応し、経験豊富なスタッフが丁寧に搬出作業を行います。不要品の中に価値ある品があれば、その場で査定して買取対応も可能なため、処分費用の節約につながる場合もあります。</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>https://koyorecycle.com/</t>
+          <t>https://itabashi-hikawa-lib.jp/</t>
         </is>
       </c>
     </row>
@@ -31116,72 +31100,72 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>company-6234</t>
+          <t>company-31483</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>栃木不用品回収センター</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/tochigi-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/tochigi-fuyouhin.png</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>栃木不用品回収センター</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>4.42 （ 7 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>栃木不用品回収センターは、栃木県全域に対応する地域密着型の不用品回収専門業者です。宇都宮市を拠点に、問い合わせから最短25分で現地到着する迅速な対応力が強みで、365日24時間受付・即日回収にも対応しています。見積もり後の追加費用が発生しない明朗な料金体系を採用し、15年以上の実績と高いリピート率を誇ります。家庭用品から事業系廃棄物、遺品整理まで幅広く対応し、丁寧で安心感のある作業も特徴です。</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+          <t>基本プラン：4,900円～ / 軽トラお任せパック：9,900円～ / 1.5t車両コース：19,900円～ / 2t車両コース：50,000円～ / 4t大型車両コース：100,000円～ / オーダーメイドプラン：お見積り</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの最新の口コミ</t>
+          <t>栃木不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>40代 男性</t>
+          <t>30代・女性</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -31196,72 +31180,72 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+          <t>子どもの成長に伴い、使わなくなったベビー用品やおもちゃが増えたため利用しました。自分では分別や運び出しが難しかったのですが、スタッフの方が手際よく対応してくれて短時間で片付きました。重たい物も無理なく搬出してもらえ、育児中でも負担が少なかったです。問い合わせから回収までの流れも分かりやすく、安心してお願いできました。</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/tochigi-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/tochigi-fuyouhin.png</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの評判・口コミ</t>
+          <t>栃木不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+          <t>15年以上の実績あり / 買取制度あり / 追加費用なしで安心</t>
         </is>
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>栃木不用品回収センターは、栃木県全域に対応する地域密着型の不用品回収専門業者です。宇都宮市を拠点に、問い合わせから最短25分で現地到着する迅速な対応力が強みで、365日24時間受付・即日回収にも対応しています。見積もり後の追加費用が発生しない明朗な料金体系を採用し、15年以上の実績と高いリピート率を誇ります。家庭用品から事業系廃棄物、遺品整理まで幅広く対応し、丁寧で安心感のある作業も特徴です。</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>https://otasuke-master.co.jp/</t>
+          <t>https://abc-project.tochigi.jp/</t>
         </is>
       </c>
     </row>
@@ -31274,37 +31258,37 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>company-8102</t>
+          <t>company-31547</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>茨城不用品回収センター</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/ibaraki-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/ibaraki-fuyouhinkaisyu.png</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>茨城不用品回収センター</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>4.75 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -31314,47 +31298,47 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>茨城不用品回収センターは、茨城県内全域（例：水戸市、つくば市、日立市など）を対象にした地域密着の不用品回収サービスです。家具・家電から粗大ゴミ、倉庫や納屋の大量片付けまで広く対応し、24時間365日受付・即日対応も可能なフットワークの軽さが強みです。定額パックや明確な料金体系で後から追加請求がなく、現地見積もりや搬出作業もスタッフが行います。また地方ならではの農機具や工具の買取にも対応し、回収費用を抑える工夫も行っています。回収後は分別・リサイクル処理も徹底し、環境負荷低減にも配慮したサービスです。</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+          <t>SSパック：4,800円～ / Sパック：9,800円～ / Mパック：19,800円～ / Lパック：42,800円～ / LLパック：85,800円～ / その他：別途お見積り</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>片付け堂の最新の口コミ</t>
+          <t>茨城不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>50代・女性</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+          <t>父が亡くなり、その後母が老人ホームへ入所することになったため、長年暮らしてきた実家の整理をお願いしました。思い出の品が多く、処分の判断に迷う場面もありましたが、スタッフの方が急かすことなく丁寧に確認してくださり、気持ちの整理もしながら進めることができました。重たい家具や家電もすべて任せられ、家族への負担を減らせた点もありがたかったです。安心してお願いできる業者だと感じました。</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -31364,27 +31348,27 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/ibaraki-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/ibaraki-fuyouhinkaisyu.png</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>片付け堂の評判・口コミ</t>
+          <t>茨城不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
@@ -31394,12 +31378,12 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr">
@@ -31409,17 +31393,17 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+          <t>茨城県内なら最短30分でお伺い / 買取制度ありで費用圧縮 / 特殊清掃などオプションサービスも豊富</t>
         </is>
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>茨城不用品回収センターは、茨城県内全域（例：水戸市、つくば市、日立市など）を対象にした地域密着の不用品回収サービスです。家具・家電から粗大ゴミ、倉庫や納屋の大量片付けまで広く対応し、24時間365日受付・即日対応も可能なフットワークの軽さが強みです。定額パックや明確な料金体系で後から追加請求がなく、現地見積もりや搬出作業もスタッフが行います。また地方ならではの農機具や工具の買取にも対応し、回収費用を抑える工夫も行っています。回収後は分別・リサイクル処理も徹底し、環境負荷低減にも配慮したサービスです。</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>https://www.katazukedou.com/</t>
+          <t>https://commit-hiroba.net/</t>
         </is>
       </c>
     </row>
@@ -31432,27 +31416,27 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>company-3871</t>
+          <t>company-31560</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>不用品回収コスモ東京</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/cosmo-tokyo/</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/cosmo-tokyo.png</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>不用品回収コスモ東京</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -31462,42 +31446,42 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>5 （ 3 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>不用品回収コスモ東京は、東京都内を中心に対応する不用品回収専門業者です。家具・家電・生活用品などの回収をはじめ、引っ越しや住み替えに伴う大量回収にも柔軟に対応しています。現地見積もりは無料で、回収内容を確認したうえで金額を提示する明朗な料金体系を採用。分別や搬出作業もスタッフが行うため、手間をかけずに片付けを進められる点が特徴です。状態の良い不用品は買取相談も可能で、費用を抑えたい方にも利用されています。</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+          <t>軽トラパック：9,800円～ / 1.5tトラックパック：29,800円～ / 2tトラックパック：49,800円～ / 2tロングパック：88,000円～ / それ以上の回収：要お見積り</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>福島片付け110番の最新の口コミ</t>
+          <t>不用品回収コスモ東京の最新の口コミ</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>40代・男性</t>
+          <t>30代・男性</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -31507,12 +31491,12 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+          <t>引っ越しを控えて不要な家具や家電が一度に出たため利用しました。自治体回収だと日程が合わず困っていましたが、見積もりから回収までの流れがスムーズで助かりました。当日も時間通りに来てくれ、手際よく搬出してもらえたので予定が立てやすかったです。引っ越し準備に集中できた点が特に良かったと感じています。</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
@@ -31522,17 +31506,17 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/cosmo-tokyo/</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/cosmo-tokyo.png</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>福島片付け110番の評判・口コミ</t>
+          <t>不用品回収コスモ東京の評判・口コミ</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
@@ -31547,12 +31531,12 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
@@ -31567,17 +31551,17 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+          <t>東京都内全域に対応 / 現地見積もり無料 / 嬉しい高価買取実績多数</t>
         </is>
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>不用品回収コスモ東京は、東京都内を中心に対応する不用品回収専門業者です。家具・家電・生活用品などの回収をはじめ、引っ越しや住み替えに伴う大量回収にも柔軟に対応しています。現地見積もりは無料で、回収内容を確認したうえで金額を提示する明朗な料金体系を採用。分別や搬出作業もスタッフが行うため、手間をかけずに片付けを進められる点が特徴です。状態の良い不用品は買取相談も可能で、費用を抑えたい方にも利用されています。</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
         <is>
-          <t>https://fukushima-kataduke110ban.com/</t>
+          <t>https://huyouhin-tokyo.co.jp/</t>
         </is>
       </c>
     </row>
@@ -31590,87 +31574,87 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>company-3850</t>
+          <t>company-31579</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>京都不用品回収センター</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/kyoto-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/kyoto-fuyouhin.png</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>京都不用品回収センター</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>4.5 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>京都不用品回収センターは、京都市を中心に不用品・粗大ゴミの回収サービスを提供する業者です。無料の現地見積もりや明朗な料金体系で、分かりやすく安心して依頼できます。徹底した分別とリユース・リサイクルにより処分コストを抑え、再利用可能な品は買取査定も実施。柔軟な日時対応や追加費用なしの安心サービスで、少量から大量まで幅広く対応しています。地域評価も高い実績を誇ります。</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>福島県 / 茨城県</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
+          <t>SSパック：4,800円～ / Sパック：9,800円～ / Mパック：19,800円～ / Lパック：42,800円～ / LLパック：85,800円～ / 見積もりパック：ご相談ください</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>フロンティアグループの最新の口コミ</t>
+          <t>京都不用品回収センターの最新の口コミ</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>30歳・男性</t>
+          <t>50代・男性</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度4・対応4）</t>
+          <t>（回収料金4.5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
+          <t>実家の遺品整理をすることになり、自分一人では手に負えず京都不用品回収センターに相談しました。遺品整理ということで不安もありましたが、スタッフの方が終始落ち着いた対応で、こちらの気持ちにも配慮しながら作業を進めてくれたのが印象的です。処分する物と残す物を丁寧に確認してくれたので、安心して任せることができました。時間も思ったよりかからず、お願いして本当に良かったです。</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
@@ -31680,62 +31664,62 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/kyoto-fuyouhinkaisyu/</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/01/kyoto-fuyouhin.png</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>フロンティアグループの評判・口コミ</t>
+          <t>京都不用品回収センターの評判・口コミ</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+          <t>安心の地域密着型 / 嬉しい買取査定あり / 明朗な料金体系</t>
         </is>
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>京都不用品回収センターは、京都市を中心に不用品・粗大ゴミの回収サービスを提供する業者です。無料の現地見積もりや明朗な料金体系で、分かりやすく安心して依頼できます。徹底した分別とリユース・リサイクルにより処分コストを抑え、再利用可能な品は買取査定も実施。柔軟な日時対応や追加費用なしの安心サービスで、少量から大量まで幅広く対応しています。地域評価も高い実績を誇ります。</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>https://iwaki-benriya.com/</t>
+          <t>https://totteoki-geijutsu.com/</t>
         </is>
       </c>
     </row>
@@ -31748,27 +31732,27 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>company-615</t>
+          <t>company-428</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -31778,7 +31762,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>4.75 （ 4 件 ）</t>
+          <t>4.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -31788,67 +31772,67 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+          <t>不用品整理：要見積もり</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>エコスピードの最新の口コミ</t>
+          <t>未来応援隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>30代 女性</t>
+          <t>20歳・男性</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>エコスピードの評判・口コミ</t>
+          <t>未来応援隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
@@ -31858,19 +31842,19 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
           <t>4.75</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
       <c r="AB202" t="inlineStr">
         <is>
           <t>4.75</t>
@@ -31878,22 +31862,22 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
         </is>
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>https://eco-speed.life/</t>
+          <t>https://www.miraiouentai.com/</t>
         </is>
       </c>
     </row>
@@ -31906,27 +31890,27 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>company-3839</t>
+          <t>company-632</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -31936,42 +31920,42 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>東京都 / 神奈川県</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の最新の口コミ</t>
+          <t>フレッシュマンサービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>70代・女性</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
@@ -31986,7 +31970,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
@@ -31996,17 +31980,17 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の評判・口コミ</t>
+          <t>フレッシュマンサービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X203" t="inlineStr">
@@ -32021,7 +32005,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -32041,17 +32025,17 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
         </is>
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+          <t>https://www.freshman-s.com/</t>
         </is>
       </c>
     </row>
@@ -32064,150 +32048,1572 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
+          <t>company-2133</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>片付け侍</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>片付け侍</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>4.57 （ 7 件 ）</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>片付け侍の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>29歳・男性</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応3.5）</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>片付け侍の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>https://katazuke-s.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>14</v>
+      </c>
+      <c r="B205" t="n">
+        <v>9</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>company-4087</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ECO助っ人</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>ECO助っ人</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>3.91 （ 6 件 ）</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>ECO助っ人の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>57歳・女性</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度3.5・対応3）</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>ECO助っ人の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>https://eco-suketto.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>14</v>
+      </c>
+      <c r="B206" t="n">
+        <v>10</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>company-380</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>3.87 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>63歳・女性</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度4・対応5）</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>https://koyorecycle.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>14</v>
+      </c>
+      <c r="B207" t="n">
+        <v>11</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>company-6234</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスター</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスター</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>4.42 （ 7 件 ）</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>40代 男性</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>https://otasuke-master.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>14</v>
+      </c>
+      <c r="B208" t="n">
+        <v>12</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>company-8102</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>片付け堂</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>片付け堂</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>5 （ 2 件 ）</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>片付け堂の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>片付け堂の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>https://www.katazukedou.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>14</v>
+      </c>
+      <c r="B209" t="n">
+        <v>13</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>company-3871</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>福島片付け110番</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>福島片付け110番</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>5 （ 3 件 ）</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>福島片付け110番の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>40代・男性</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>福島片付け110番の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>https://fukushima-kataduke110ban.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>14</v>
+      </c>
+      <c r="B210" t="n">
+        <v>14</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>company-3850</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>4.5 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>福島県 / 茨城県</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>フロンティアグループの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>30歳・男性</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度4・対応4）</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>フロンティアグループの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>https://iwaki-benriya.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>14</v>
+      </c>
+      <c r="B211" t="n">
+        <v>15</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>company-615</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>4.75 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>エコスピードの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>30代 女性</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>エコスピードの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>https://eco-speed.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>15</v>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>company-3839</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>5 （ 1 件 ）</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>15</v>
+      </c>
+      <c r="B213" t="n">
+        <v>2</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
           <t>company-418</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
         <is>
           <t>5 （ 2 件 ）</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
+      <c r="J213" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t>深夜・早朝の回収 / 即日対応 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t>福岡県 / 長崎県</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr">
+      <c r="N213" t="inlineStr">
         <is>
           <t>単品回収：1点1,000円より</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr">
+      <c r="O213" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の最新の口コミ</t>
         </is>
       </c>
-      <c r="P204" t="inlineStr">
+      <c r="P213" t="inlineStr">
         <is>
           <t>59歳・女性</t>
         </is>
       </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
         <is>
           <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
-      <c r="S204" t="inlineStr">
+      <c r="S213" t="inlineStr">
         <is>
           <t>問い合わせの迅速な対応。当日も親切に対応していただきました。また機会があれば利用したいと思います。ありがとうございました。</t>
         </is>
       </c>
-      <c r="T204" t="inlineStr">
+      <c r="T213" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="U213" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
+      <c r="V213" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="W204" t="inlineStr">
+      <c r="W213" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の評判・口コミ</t>
         </is>
       </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
         <is>
           <t>2件</t>
         </is>
       </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
         <is>
           <t>1点から不用品を回収してもらえる / 引越しとセットで依頼するとお得 / LINEでスピード見積もりに対応</t>
         </is>
       </c>
-      <c r="AE204" t="inlineStr">
+      <c r="AE213" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="AF204" t="inlineStr"/>
+      <c r="AF213" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -5223,7 +5223,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>宮城県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 岐阜県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 長崎県</t>
+          <t>宮城県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 長崎県</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -16585,7 +16585,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>福井県 / 京都府 / 滋賀県</t>
+          <t>福井県 / 滋賀県 / 京都府</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -17963,12 +17963,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -17998,7 +17998,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>30代・女性</t>
+          <t>50代・女性</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>エレベーターがない4階からベッドを素早く運んでくださり、さすがだなと思いました。直前に予定が入ってしまい、時間をずらしてもらいましたが、とても丁寧に対応してもらえました。こちらに頼んで良かったです。また何かあったらお願いしたいと思います。</t>
+          <t>主人を亡くしてから、ずっと手を付けられずにいた遺品の整理をお願いしました。スタッフの方が終始丁寧で、思い出の品の扱いにも配慮してくれたので、気持ちが軽くなりました。見積もりの時から不安なく進められ、納得のいく形で整理が完了。心の整理にもつながるサービスでした。</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2025/01/fuyouhinkaisyucenter-kobe.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2025/01/kobe-fuyouhin.png</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2025/01/fuyouhinkaisyucenter-kobe.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2025/01/kobe-fuyouhin.png</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>富山県 / 石川県 / 福井県 / 岐阜県 / 京都府 / 滋賀県</t>
+          <t>富山県 / 石川県 / 福井県 / 岐阜県 / 滋賀県 / 京都府</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -20925,7 +20925,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>東京都 / 埼玉県 / 神奈川県 / 千葉県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県</t>
+          <t>東京都 / 埼玉県 / 神奈川県 / 千葉県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>京都府 / 滋賀県</t>
+          <t>滋賀県 / 京都府</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -24241,7 +24241,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県</t>
+          <t>大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県</t>
+          <t>大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>大阪府 / 京都府 / 滋賀県 / 兵庫県</t>
+          <t>大阪府 / 滋賀県 / 京都府 / 兵庫県</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -24715,7 +24715,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>大阪府 / 京都府 / 滋賀県</t>
+          <t>大阪府 / 滋賀県 / 京都府</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>北海道 / 東京都 / 神奈川県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 三重県</t>
+          <t>北海道 / 東京都 / 神奈川県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 三重県</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県</t>
+          <t>大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -25813,7 +25813,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -27227,7 +27227,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>宮城県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 山梨県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県</t>
+          <t>宮城県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 山梨県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -29423,7 +29423,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -30150,16 +30150,7 @@
       </c>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>https://sakado-yousan.com/＂&gt;https://sakado-yousan.com/&lt;/a&gt;&lt;/td&gt;
-            &lt;/tr&gt;
-			     &lt;tr&gt;
-            &lt;th&gt;GoogleMap&lt;/th&gt;
-              &lt;td&gt;&lt;/td&gt;
-            &lt;/tr&gt;
-          &lt;/tbody&gt;
-        &lt;/table&gt;
-      &lt;/section&gt;
-      &lt;section id=</t>
+          <t>https://sakado-yousan.com/</t>
         </is>
       </c>
     </row>
@@ -32098,7 +32089,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -32256,7 +32247,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -32572,7 +32563,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 京都府 / 滋賀県 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF213"/>
+  <dimension ref="A1:AF221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31723,47 +31723,43 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>company-428</t>
+          <t>company-31665</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>ライフサポート俱楽部</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/life-support-club/</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/life-support-club.png</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>ライフサポート俱楽部</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>4.87 （ 4 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>茨城県古河市を中心に不用品回収・粗大ごみの処分を行う地域密着型サービスです。 一般廃棄物収集運搬許可を持ち、家具・家電などの少量〜大量回収に対応。 遺品整理や孤独死現場の片付けなど特殊な案件にも対応可能で、現地確認による適正な見積もり提示と丁寧な作業が特徴です。</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -31771,104 +31767,56 @@
           <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>静岡県</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>不用品整理：要見積もり</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>未来応援隊の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>20歳・男性</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度4・対応5）</t>
-        </is>
-      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr">
         <is>
-          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
-        </is>
-      </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/life-support-club/</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/life-support-club.png</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>未来応援隊の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
+          <t>ライフサポート俱楽部の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr"/>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
+          <t>一般廃棄物収集運搬許可業者で安心 / 少量から大量回収まで柔軟に対応可能 / 遺品整理・特殊清掃にも対応可能</t>
         </is>
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>茨城県古河市を中心に不用品回収・粗大ごみの処分を行う地域密着型サービスです。 一般廃棄物収集運搬許可を持ち、家具・家電などの少量〜大量回収に対応。 遺品整理や孤独死現場の片付けなど特殊な案件にも対応可能で、現地確認による適正な見積もり提示と丁寧な作業が特徴です。</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>https://www.miraiouentai.com/</t>
+          <t>https://life-support-club.com/</t>
         </is>
       </c>
     </row>
@@ -31881,152 +31829,104 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>company-632</t>
+          <t>company-32023</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>未来産業</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/miraisangyo/</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/miraisangyou.png</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>未来産業</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>来産業は茨城県常総市を拠点とする不用品回収・片付け業者です。 一般家庭〜企業までの不要品回収・処分・買取だけでなく、ゴミ屋敷の片付けや遺品整理にも対応します。 古物商や遺品整理士など資格取得済みで、複数自治体の一般廃棄物収集運搬許可・産業廃棄物収集運搬許可を保有し、適正処理に基づいた回収を行います。見積り無料で安心して依頼できる点が特徴です。</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>即日対応 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>東京都 / 神奈川県</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>フレッシュマンサービスの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>70代・女性</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
-        </is>
-      </c>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr">
         <is>
-          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
-        </is>
-      </c>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/miraisangyo/</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/miraisangyou.png</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>未来産業の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>2件</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
+          <t>許可取得済みの正規回収業者 / 不用品回収から遺品整理・ゴミ屋敷片付けまで幅広く対応可能 / 無料出張見積り・買取対応によるコスト軽減</t>
         </is>
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>来産業は茨城県常総市を拠点とする不用品回収・片付け業者です。 一般家庭〜企業までの不要品回収・処分・買取だけでなく、ゴミ屋敷の片付けや遺品整理にも対応します。 古物商や遺品整理士など資格取得済みで、複数自治体の一般廃棄物収集運搬許可・産業廃棄物収集運搬許可を保有し、適正処理に基づいた回収を行います。見積り無料で安心して依頼できる点が特徴です。</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>https://www.freshman-s.com/</t>
+          <t>https://miraisangyou.jp/</t>
         </is>
       </c>
     </row>
@@ -32039,152 +31939,100 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>company-2133</t>
+          <t>company-32030</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>LIFENECT</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/lifenect/</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/lifenect-kitaibaraki.png</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>片付け侍</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>LIFENECT</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>4.57 （ 7 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>茨城県北茨城市・高萩市を中心に不用品回収や家具家電の処分、遺品整理を手掛ける地域密着型サービスです。 重くて運べない大型家具や衣類などの回収に対応し、引越しで出た粗大ゴミの片付けも受け付けています。 また、ご家庭の困りごとを支える家事代行サービス（お墓参り・草刈りなど）も提供し、幅広い暮らしのサポートを行います。</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>片付け侍の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>29歳・男性</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応3.5）</t>
-        </is>
-      </c>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr">
         <is>
-          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
-        </is>
-      </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/lifenect/</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/lifenect-kitaibaraki.png</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>片付け侍の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
-      </c>
+          <t>LIFENECTの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>7件</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+          <t>地域密着型の不用品回収・処分サービス / 遺品整理や大型家具・衣類回収に対応可能 / 家事代行サービスと併せた暮らしのサポート</t>
         </is>
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>茨城県北茨城市・高萩市を中心に不用品回収や家具家電の処分、遺品整理を手掛ける地域密着型サービスです。 重くて運べない大型家具や衣類などの回収に対応し、引越しで出た粗大ゴミの片付けも受け付けています。 また、ご家庭の困りごとを支える家事代行サービス（お墓参り・草刈りなど）も提供し、幅広い暮らしのサポートを行います。</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>https://katazuke-s.com/</t>
+          <t>https://www.lifenect-kitaibaraki.com/</t>
         </is>
       </c>
     </row>
@@ -32197,152 +32045,108 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>company-4087</t>
+          <t>company-32033</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>おたすけ悟空</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/otasuke59/</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/otasuke59.png</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+          <t>おたすけ悟空</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
-          <t>3.91 （ 6 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>おたすけ悟空は茨城県内を中心に不用品回収・粗大ゴミ処分を行う地域密着型サービスです。 家具・家電・生活用品などの単品回収から、引越しや大掃除に伴う大量処分まで幅広く対応します。 見積り無料で追加料金なしの明朗会計を掲げ、即日対応や分別代行にも対応可能。</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>東京都 / 埼玉県 / 茨城県</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
-        </is>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>ECO助っ人の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>57歳・女性</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度3.5・対応3）</t>
-        </is>
-      </c>
+          <t>お得なプランA (軽トラック)：25,000～ / お得なプランB ( 1t )：48,000～ / お得なプランC ( 2t )：88,000～ / 他社圧倒プラン( 4t )：148,000～</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr">
         <is>
-          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
-        </is>
-      </c>
-      <c r="T205" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/otasuke59/</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/otasuke59.png</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>ECO助っ人の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
-      </c>
+          <t>おたすけ悟空の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>6件</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+          <t>地域密着型の不用品回収・粗大ごみ処分サービス / 即日対応や分別代行によるスムーズな片付け / 無料見積り・明朗会計による安心感</t>
         </is>
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>おたすけ悟空は茨城県内を中心に不用品回収・粗大ゴミ処分を行う地域密着型サービスです。 家具・家電・生活用品などの単品回収から、引越しや大掃除に伴う大量処分まで幅広く対応します。 見積り無料で追加料金なしの明朗会計を掲げ、即日対応や分別代行にも対応可能。</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>https://eco-suketto.jp/</t>
+          <t>https://otasuke59.com/</t>
         </is>
       </c>
     </row>
@@ -32355,152 +32159,100 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>company-380</t>
+          <t>company-32042</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>クマさん回収センター</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/benriya903-tsukuba/</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/benriya903-tsukuba.png</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+          <t>クマさん回収センター</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>3.87 （ 4 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>つくば不用品回収クマさん回収センターは、茨城県つくば市を中心に、土浦・牛久・つくばみらいの広いエリアで不用品や粗大ごみの回収・処分を行う地域密着型サービスです。 家具・家電から引越し後の大量ゴミ、店舗・事務所の片付けまで幅広く対応しているほか、遺品整理やゴミ屋敷の片付けにも対応。 女性スタッフ常駐や独自のリサイクル体制を通じた低価格サービスが特徴です。</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
-        </is>
-      </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>紅葉リサイクル福岡の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>63歳・女性</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度4・対応5）</t>
-        </is>
-      </c>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr">
         <is>
-          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
-        </is>
-      </c>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/benriya903-tsukuba/</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/benriya903-tsukuba.png</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>3.87</t>
-        </is>
-      </c>
+          <t>クマさん回収センターの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>3.87</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+          <t>24時間対応の地域密着型不用品回収・粗大ごみ処分 / 家具・家電・事務所片付けから遺品整理・ゴミ屋敷片付けまで幅広く対応可能 / 女性スタッフ対応とリサイクル重視による安心・低価格サービス</t>
         </is>
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>つくば不用品回収クマさん回収センターは、茨城県つくば市を中心に、土浦・牛久・つくばみらいの広いエリアで不用品や粗大ごみの回収・処分を行う地域密着型サービスです。 家具・家電から引越し後の大量ゴミ、店舗・事務所の片付けまで幅広く対応しているほか、遺品整理やゴミ屋敷の片付けにも対応。 女性スタッフ常駐や独自のリサイクル体制を通じた低価格サービスが特徴です。</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
         <is>
-          <t>https://koyorecycle.com/</t>
+          <t>https://benriya903-tsukuba.com/</t>
         </is>
       </c>
     </row>
@@ -32513,152 +32265,104 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>company-6234</t>
+          <t>company-32047</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>金和国際株式会社</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/kinwa-international/</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/kinwa-international.png</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>金和国際株式会社</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
-          <t>4.42 （ 7 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品回収・粗大ごみ処分、遺品整理・特殊清掃など、生活に関わる幅広い片付けサービスを提供する業者です。 一般家庭だけでなく法人・店舗・事務所の廃棄品処理にも対応し、産業廃棄物・一般廃棄物の収集運搬許可を保有。 現地見積りを無料で行い、見積もり後の追加費用なしの明朗会計を掲げています。</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>即日対応 / 買取対応 / 単品回収可能</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>便利屋お助けマスターの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>40代 男性</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
-        </is>
-      </c>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr">
         <is>
-          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
-        </is>
-      </c>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/kinwa-international/</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/kinwa-international.png</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
+          <t>金和国際株式会社の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>7件</t>
-        </is>
-      </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+          <t>許可取得済みの正規回収業者 / 不用品回収・遺品整理・特殊清掃まで幅広く対応可能 / 無料現地見積りと追加費用なしの明朗会計</t>
         </is>
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品回収・粗大ごみ処分、遺品整理・特殊清掃など、生活に関わる幅広い片付けサービスを提供する業者です。 一般家庭だけでなく法人・店舗・事務所の廃棄品処理にも対応し、産業廃棄物・一般廃棄物の収集運搬許可を保有。 現地見積りを無料で行い、見積もり後の追加費用なしの明朗会計を掲げています。</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>https://otasuke-master.co.jp/</t>
+          <t>https://kinwa-international.com/</t>
         </is>
       </c>
     </row>
@@ -32671,152 +32375,104 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>company-8102</t>
+          <t>company-32051</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>ネセサリー</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/recycle-necessary/</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/recycle-necessary.png</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>片付け堂</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>ネセサリー</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>家具・家電・生活用品などの日常的な不要品だけでなく、引越しに伴う大量処分・倉庫整理にも対応しており、出張見積りは無料。 一般廃棄物収集運搬許可を保有しており、適正な処理ルートにて回収を行います。 地域密着型の対応や丁寧な作業、臨機応変なスケジュール調整が強みで、迅速・安心の片付けを提供しています。</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>片付け堂の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P208" t="inlineStr">
-        <is>
-          <t>60代・女性</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R208" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
-        </is>
-      </c>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr">
         <is>
-          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
-        </is>
-      </c>
-      <c r="T208" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/recycle-necessary/</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/recycle-necessary.png</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>片付け堂の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>ネセサリーの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>2件</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
       <c r="AD208" t="inlineStr">
         <is>
-          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+          <t>許可取得済みの正規回収業者 / 家具・家電・大量処分まで幅広く対応可能 / 無料出張見積りによる安心価格提示</t>
         </is>
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>家具・家電・生活用品などの日常的な不要品だけでなく、引越しに伴う大量処分・倉庫整理にも対応しており、出張見積りは無料。 一般廃棄物収集運搬許可を保有しており、適正な処理ルートにて回収を行います。 地域密着型の対応や丁寧な作業、臨機応変なスケジュール調整が強みで、迅速・安心の片付けを提供しています。</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
         <is>
-          <t>https://www.katazukedou.com/</t>
+          <t>https://recycle-necessary.co.jp/</t>
         </is>
       </c>
     </row>
@@ -32829,152 +32485,104 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>company-3871</t>
+          <t>company-32054</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>有限会社千代田衛生</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/chiyodaeisei/</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/chiyodaeisei.png</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>有限会社千代田衛生</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5 （ 3 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>一般家庭の不用品回収はつくば市・土浦市・かすみがうら市などの限定エリアに対応しており、小〜中規模の片付けを柔軟にサポートします。 一方、法人向けの廃棄物処理や産業廃棄物回収に関しては茨城県全域を対象としており、企業・店舗の大量廃棄物にも対応可能な点が特徴です。 現地見積りを基に最適な処理方法を提案します。</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>福島県</t>
-        </is>
-      </c>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr">
         <is>
-          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
-        </is>
-      </c>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>福島片付け110番の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>40代・男性</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R209" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度5・対応5）</t>
-        </is>
-      </c>
+          <t>2t深ダンプ：35,000円〜</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr">
         <is>
-          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
-        </is>
-      </c>
-      <c r="T209" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/chiyodaeisei/</t>
         </is>
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/chiyodaeisei.png</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>福島片付け110番の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>有限会社千代田衛生の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>3件</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>4.66</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+          <t>許可取得済みの正規回収・廃棄物処理業者 / 一般家庭と法人で対応エリアを明確に区分 / 不用品回収・遺品整理・産業廃棄物回収まで幅広く対応可能</t>
         </is>
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>一般家庭の不用品回収はつくば市・土浦市・かすみがうら市などの限定エリアに対応しており、小〜中規模の片付けを柔軟にサポートします。 一方、法人向けの廃棄物処理や産業廃棄物回収に関しては茨城県全域を対象としており、企業・店舗の大量廃棄物にも対応可能な点が特徴です。 現地見積りを基に最適な処理方法を提案します。</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>https://fukushima-kataduke110ban.com/</t>
+          <t>https://chiyodaeisei.com/</t>
         </is>
       </c>
     </row>
@@ -32987,27 +32595,27 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>company-3850</t>
+          <t>company-428</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -33017,7 +32625,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>4.5 （ 4 件 ）</t>
+          <t>4.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -33027,47 +32635,47 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>福島県 / 茨城県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
+          <t>不用品整理：要見積もり</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>フロンティアグループの最新の口コミ</t>
+          <t>未来応援隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>30歳・男性</t>
+          <t>20歳・男性</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度4・対応4）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
+          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
@@ -33077,17 +32685,17 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>フロンティアグループの評判・口コミ</t>
+          <t>未来応援隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
@@ -33097,7 +32705,7 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
@@ -33107,32 +32715,32 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
         </is>
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>https://iwaki-benriya.com/</t>
+          <t>https://www.miraiouentai.com/</t>
         </is>
       </c>
     </row>
@@ -33145,72 +32753,72 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>company-615</t>
+          <t>company-632</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>4.75 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+          <t>東京都 / 神奈川県</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>エコスピードの最新の口コミ</t>
+          <t>フレッシュマンサービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>30代 女性</t>
+          <t>70代・女性</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -33225,7 +32833,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
@@ -33235,62 +32843,62 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>エコスピードの評判・口コミ</t>
+          <t>フレッシュマンサービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
         </is>
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>https://eco-speed.life/</t>
+          <t>https://www.freshman-s.com/</t>
         </is>
       </c>
     </row>
@@ -33303,152 +32911,152 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>company-3839</t>
+          <t>company-2133</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>4.57 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の最新の口コミ</t>
+          <t>片付け侍の最新の口コミ</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>29歳・男性</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度5・対応3.5）</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の評判・口コミ</t>
+          <t>片付け侍の評判・口コミ</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
         </is>
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+          <t>https://katazuke-s.com/</t>
         </is>
       </c>
     </row>
@@ -33461,150 +33069,1414 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
+          <t>company-4087</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ECO助っ人</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ECO助っ人</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>3.91 （ 6 件 ）</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>ECO助っ人の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>57歳・女性</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度3.5・対応3）</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>ECO助っ人の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>https://eco-suketto.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>15</v>
+      </c>
+      <c r="B214" t="n">
+        <v>3</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>company-380</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>3.87 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>63歳・女性</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度4・対応5）</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>https://koyorecycle.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>15</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>company-6234</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスター</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスター</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>4.42 （ 7 件 ）</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>40代 男性</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>https://otasuke-master.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>15</v>
+      </c>
+      <c r="B216" t="n">
+        <v>5</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>company-8102</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>片付け堂</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>片付け堂</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>5 （ 2 件 ）</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>片付け堂の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>片付け堂の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>https://www.katazukedou.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>15</v>
+      </c>
+      <c r="B217" t="n">
+        <v>6</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>company-3871</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>福島片付け110番</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>福島片付け110番</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>5 （ 3 件 ）</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>福島片付け110番の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>40代・男性</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>福島片付け110番の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>https://fukushima-kataduke110ban.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>15</v>
+      </c>
+      <c r="B218" t="n">
+        <v>7</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>company-3850</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>4.5 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>福島県 / 茨城県</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>フロンティアグループの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>30歳・男性</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度4・対応4）</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>フロンティアグループの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>https://iwaki-benriya.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>15</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>company-615</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>4.75 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>エコスピードの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>30代 女性</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>エコスピードの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>https://eco-speed.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>15</v>
+      </c>
+      <c r="B220" t="n">
+        <v>9</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>company-3839</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>5 （ 1 件 ）</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>15</v>
+      </c>
+      <c r="B221" t="n">
+        <v>10</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
           <t>company-418</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
         <is>
           <t>5 （ 2 件 ）</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
+      <c r="J221" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t>深夜・早朝の回収 / 即日対応 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t>福岡県 / 長崎県</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr">
+      <c r="N221" t="inlineStr">
         <is>
           <t>単品回収：1点1,000円より</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr">
+      <c r="O221" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の最新の口コミ</t>
         </is>
       </c>
-      <c r="P213" t="inlineStr">
+      <c r="P221" t="inlineStr">
         <is>
           <t>59歳・女性</t>
         </is>
       </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R213" t="inlineStr">
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
         <is>
           <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
-      <c r="S213" t="inlineStr">
+      <c r="S221" t="inlineStr">
         <is>
           <t>問い合わせの迅速な対応。当日も親切に対応していただきました。また機会があれば利用したいと思います。ありがとうございました。</t>
         </is>
       </c>
-      <c r="T213" t="inlineStr">
+      <c r="T221" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="U221" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="V213" t="inlineStr">
+      <c r="V221" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="W213" t="inlineStr">
+      <c r="W221" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の評判・口コミ</t>
         </is>
       </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
         <is>
           <t>2件</t>
         </is>
       </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
         <is>
           <t>1点から不用品を回収してもらえる / 引越しとセットで依頼するとお得 / LINEでスピード見積もりに対応</t>
         </is>
       </c>
-      <c r="AE213" t="inlineStr">
+      <c r="AE221" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="AF213" t="inlineStr"/>
+      <c r="AF221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF221"/>
+  <dimension ref="A1:AF223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32595,47 +32595,43 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>company-428</t>
+          <t>company-32417</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>丸善エコアース有限会社</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/maruzen/</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/maruzen.png</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>丸善エコアース有限会社</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>4.87 （ 4 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>茨城県日立市を拠点に、不用品回収・粗大ごみ処分や一般廃棄物・産業廃棄物処理を手がける地域密着型サービスです。 家庭の不要品から事務所や店舗の大量廃棄物まで対応し、引越しに伴う片付けや倉庫整理、大型家具・家電の回収にも対応します。 一般廃棄物収集運搬許可や産業廃棄物収集運搬許可を保有しており、適正処理による安全な廃棄を行う点が特徴です。</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -32645,102 +32641,58 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>静岡県</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>不用品整理：要見積もり</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>未来応援隊の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>20歳・男性</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="R210" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度4・対応5）</t>
-        </is>
-      </c>
+          <t>茨城県 / 千葉県</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr">
         <is>
-          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
-        </is>
-      </c>
-      <c r="T210" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/maruzen/</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/maruzen.png</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>未来応援隊の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
+          <t>丸善エコアース有限会社の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
+          <t>許可取得済みの正規回収・廃棄物処理業者 / 家庭〜事務所・店舗まで幅広い廃棄物に対応可能 / 無料見積り・状況に合わせたプラン提案</t>
         </is>
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>茨城県日立市を拠点に、不用品回収・粗大ごみ処分や一般廃棄物・産業廃棄物処理を手がける地域密着型サービスです。 家庭の不要品から事務所や店舗の大量廃棄物まで対応し、引越しに伴う片付けや倉庫整理、大型家具・家電の回収にも対応します。 一般廃棄物収集運搬許可や産業廃棄物収集運搬許可を保有しており、適正処理による安全な廃棄を行う点が特徴です。</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>https://www.miraiouentai.com/</t>
+          <t>http://www.maruzen5383.com/</t>
         </is>
       </c>
     </row>
@@ -32753,152 +32705,104 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>company-632</t>
+          <t>company-32419</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>Oshite</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/oshite/</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/oshite.png</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Oshite</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>茨城県小美玉市を拠点に、不用品・粗大ごみ回収や一般廃棄物・産業廃棄物・特別管理廃棄物の処理を行う正規許可業者です。 家庭の粗大ごみや家電だけでなく、廃材・木屑・古紙回収やガス器具・空調機器・電線類の処理・買取など多岐にわたる回収サービスを提供。 産廃・一般廃収集運搬、法令に基づく適正処理とマニフェスト管理を実施し、広域エリアで対応しています。</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>東京都 / 神奈川県</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>フレッシュマンサービスの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>70代・女性</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R211" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
-        </is>
-      </c>
+          <t>茨城県 / 千葉県</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
-        </is>
-      </c>
-      <c r="T211" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/oshite/</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/oshite.png</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Oshiteの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>2件</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
+          <t>許可取得済みの正規回収・廃棄物処理業者 / 家庭〜事業系廃棄物まで幅広く対応可能 / 廃材・古紙・非鉄金属等の処分・買取対応</t>
         </is>
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>茨城県小美玉市を拠点に、不用品・粗大ごみ回収や一般廃棄物・産業廃棄物・特別管理廃棄物の処理を行う正規許可業者です。 家庭の粗大ごみや家電だけでなく、廃材・木屑・古紙回収やガス器具・空調機器・電線類の処理・買取など多岐にわたる回収サービスを提供。 産廃・一般廃収集運搬、法令に基づく適正処理とマニフェスト管理を実施し、広域エリアで対応しています。</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>https://www.freshman-s.com/</t>
+          <t>https://www.omitama.co.jp/index.html</t>
         </is>
       </c>
     </row>
@@ -32911,27 +32815,27 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>company-2133</t>
+          <t>company-428</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -32941,42 +32845,42 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>4.57 （ 7 件 ）</t>
+          <t>4.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
+          <t>不用品整理：要見積もり</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>片付け侍の最新の口コミ</t>
+          <t>未来応援隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>29歳・男性</t>
+          <t>20歳・男性</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -32986,12 +32890,12 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応3.5）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
+          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
@@ -33001,17 +32905,17 @@
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>片付け侍の評判・口コミ</t>
+          <t>未来応援隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
@@ -33021,42 +32925,42 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
         </is>
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>https://katazuke-s.com/</t>
+          <t>https://www.miraiouentai.com/</t>
         </is>
       </c>
     </row>
@@ -33069,87 +32973,87 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>company-4087</t>
+          <t>company-632</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>3.91 （ 6 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>東京都 / 神奈川県</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>ECO助っ人の最新の口コミ</t>
+          <t>フレッシュマンサービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>57歳・女性</t>
+          <t>70代・女性</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度3.5・対応3）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
@@ -33159,62 +33063,62 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>ECO助っ人の評判・口コミ</t>
+          <t>フレッシュマンサービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
         </is>
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
         <is>
-          <t>https://eco-suketto.jp/</t>
+          <t>https://www.freshman-s.com/</t>
         </is>
       </c>
     </row>
@@ -33227,152 +33131,152 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>company-380</t>
+          <t>company-2133</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>3.87 （ 4 件 ）</t>
+          <t>4.57 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の最新の口コミ</t>
+          <t>片付け侍の最新の口コミ</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>63歳・女性</t>
+          <t>29歳・男性</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応3.5）</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の評判・口コミ</t>
+          <t>片付け侍の評判・口コミ</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
         </is>
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
         <is>
-          <t>https://koyorecycle.com/</t>
+          <t>https://katazuke-s.com/</t>
         </is>
       </c>
     </row>
@@ -33385,122 +33289,122 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>company-6234</t>
+          <t>company-4087</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>4.42 （ 7 件 ）</t>
+          <t>3.91 （ 6 件 ）</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの最新の口コミ</t>
+          <t>ECO助っ人の最新の口コミ</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>40代 男性</t>
+          <t>57歳・女性</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度3.5・対応3）</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの評判・口コミ</t>
+          <t>ECO助っ人の評判・口コミ</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -33510,27 +33414,27 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
         </is>
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>https://otasuke-master.co.jp/</t>
+          <t>https://eco-suketto.jp/</t>
         </is>
       </c>
     </row>
@@ -33543,72 +33447,72 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>company-8102</t>
+          <t>company-380</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>3.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>片付け堂の最新の口コミ</t>
+          <t>紅葉リサイクル福岡の最新の口コミ</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>63歳・女性</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -33618,12 +33522,12 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -33633,62 +33537,62 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>片付け堂の評判・口コミ</t>
+          <t>紅葉リサイクル福岡の評判・口コミ</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
         </is>
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>https://www.katazukedou.com/</t>
+          <t>https://koyorecycle.com/</t>
         </is>
       </c>
     </row>
@@ -33701,72 +33605,72 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>company-3871</t>
+          <t>company-6234</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>5 （ 3 件 ）</t>
+          <t>4.42 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>福島片付け110番の最新の口コミ</t>
+          <t>便利屋お助けマスターの最新の口コミ</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>40代・男性</t>
+          <t>40代 男性</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -33776,12 +33680,12 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -33791,62 +33695,62 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>福島片付け110番の評判・口コミ</t>
+          <t>便利屋お助けマスターの評判・口コミ</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>https://fukushima-kataduke110ban.com/</t>
+          <t>https://otasuke-master.co.jp/</t>
         </is>
       </c>
     </row>
@@ -33859,152 +33763,152 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>company-3850</t>
+          <t>company-8102</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>5 （ 2 件 ）</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>片付け堂の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>片付け堂の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>4.5 （ 4 件 ）</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>福島県 / 茨城県</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
-        </is>
-      </c>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>フロンティアグループの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P218" t="inlineStr">
-        <is>
-          <t>30歳・男性</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度4・対応4）</t>
-        </is>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
-        </is>
-      </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>フロンティアグループの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
         </is>
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>https://iwaki-benriya.com/</t>
+          <t>https://www.katazukedou.com/</t>
         </is>
       </c>
     </row>
@@ -34017,72 +33921,72 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>company-615</t>
+          <t>company-3871</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>4.75 （ 4 件 ）</t>
+          <t>5 （ 3 件 ）</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>エコスピードの最新の口コミ</t>
+          <t>福島片付け110番の最新の口コミ</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>30代 女性</t>
+          <t>40代・男性</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -34092,77 +33996,77 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>エコスピードの評判・口コミ</t>
+          <t>福島片付け110番の評判・口コミ</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
         </is>
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>https://eco-speed.life/</t>
+          <t>https://fukushima-kataduke110ban.com/</t>
         </is>
       </c>
     </row>
@@ -34175,152 +34079,152 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>company-3839</t>
+          <t>company-3850</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フロンティアグループ</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フロンティアグループ</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>4.5 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>福島県 / 茨城県</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の最新の口コミ</t>
+          <t>フロンティアグループの最新の口コミ</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>30歳・男性</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度4・対応4）</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の評判・口コミ</t>
+          <t>フロンティアグループの評判・口コミ</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
         </is>
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
         <is>
-          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+          <t>https://iwaki-benriya.com/</t>
         </is>
       </c>
     </row>
@@ -34333,150 +34237,466 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>company-615</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>4.75 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>エコスピードの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>30代 女性</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>エコスピードの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>https://eco-speed.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>15</v>
+      </c>
+      <c r="B222" t="n">
+        <v>11</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>company-3839</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>5 （ 1 件 ）</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>15</v>
+      </c>
+      <c r="B223" t="n">
+        <v>12</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
           <t>company-418</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
         <is>
           <t>5 （ 2 件 ）</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr">
+      <c r="J223" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="K223" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t>深夜・早朝の回収 / 即日対応 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t>福岡県 / 長崎県</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr">
+      <c r="N223" t="inlineStr">
         <is>
           <t>単品回収：1点1,000円より</t>
         </is>
       </c>
-      <c r="O221" t="inlineStr">
+      <c r="O223" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の最新の口コミ</t>
         </is>
       </c>
-      <c r="P221" t="inlineStr">
+      <c r="P223" t="inlineStr">
         <is>
           <t>59歳・女性</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
         <is>
           <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
-      <c r="S221" t="inlineStr">
+      <c r="S223" t="inlineStr">
         <is>
           <t>問い合わせの迅速な対応。当日も親切に対応していただきました。また機会があれば利用したいと思います。ありがとうございました。</t>
         </is>
       </c>
-      <c r="T221" t="inlineStr">
+      <c r="T223" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="U223" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="V221" t="inlineStr">
+      <c r="V223" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="W221" t="inlineStr">
+      <c r="W223" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の評判・口コミ</t>
         </is>
       </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
         <is>
           <t>2件</t>
         </is>
       </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
         <is>
           <t>1点から不用品を回収してもらえる / 引越しとセットで依頼するとお得 / LINEでスピード見積もりに対応</t>
         </is>
       </c>
-      <c r="AE221" t="inlineStr">
+      <c r="AE223" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="AF221" t="inlineStr"/>
+      <c r="AF223" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -30616,7 +30616,7 @@
       </c>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>https://fc-sme-matching.jp/</t>
+          <t>https://www.kirari-kenko-ota.hanepyon-point.jp/</t>
         </is>
       </c>
     </row>
@@ -30770,7 +30770,7 @@
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>https://www.press-osi.com/</t>
+          <t>https://kawaguchi-shisanhinfair2019.jp/</t>
         </is>
       </c>
     </row>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF223"/>
+  <dimension ref="A1:AF226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32815,52 +32815,48 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>company-428</t>
+          <t>company-33403</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>伊豆クリーン</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/izu-clean-gyosya/</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/izuclean.png</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>伊豆クリーン</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
-          <t>4.87 （ 4 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>静岡県伊豆半島・静岡県東部エリアを中心に、不用品回収・ゴミ屋敷片付け・遺品整理などを行う片付けサービス。 家具・家電・生活用品などの不用品の回収や整理作業に対応し、未分別の状態でも仕分けから搬出までまとめて対応します。 出張見積りは無料で、買取査定を同時に行うことで回収費用の負担軽減につなげられる点が特徴です。</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -32868,99 +32864,55 @@
           <t>静岡県</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>不用品整理：要見積もり</t>
-        </is>
-      </c>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t>未来応援隊の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>20歳・男性</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度4・対応5）</t>
-        </is>
-      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/izu-clean-gyosya/</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/izuclean.png</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>未来応援隊の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
+          <t>伊豆クリーンの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
+          <t>ゴミ屋敷片付け・不用品回収・遺品整理など幅広い片付けに対応可能 / 未分別のゴミでも仕分けから搬出まで対応可能 / 不用品の買取査定により回収費用の軽減が可能</t>
         </is>
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>静岡県伊豆半島・静岡県東部エリアを中心に、不用品回収・ゴミ屋敷片付け・遺品整理などを行う片付けサービス。 家具・家電・生活用品などの不用品の回収や整理作業に対応し、未分別の状態でも仕分けから搬出までまとめて対応します。 出張見積りは無料で、買取査定を同時に行うことで回収費用の負担軽減につなげられる点が特徴です。</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>https://www.miraiouentai.com/</t>
+          <t>izuclean</t>
         </is>
       </c>
     </row>
@@ -32973,152 +32925,108 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>company-632</t>
+          <t>company-33409</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>お助けうさぎ</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/otasuke-usagi/</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/otasukeusagi.png</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>お助けうさぎ</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>不用品回収・ゴミ屋敷片付け・遺品整理・ハウスクリーニングなど、住まいの片付け全般に対応する整理サービス。 家具や家電、生活ゴミなど幅広い不用品の回収・仕分け・搬出を行い、ゴミ屋敷や汚部屋の片付けにも対応します。 さらに不用品の買取査定や清掃作業まで対応し、片付けから住環境の改善まで総合的にサポート。 関東エリアを中心に迅速な対応体制を整えており、見積り無料で相談できる点も特徴です。</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>東京都 / 神奈川県</t>
+          <t>東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 山梨県 / 静岡県</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>フレッシュマンサービスの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>70代・女性</t>
-        </is>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
-        </is>
-      </c>
+          <t>SSパック：WEB限定割引4,980円(税込) / Sパック：WEB限定割引12,800円(税込) / Mパック：WEB限定割引29,800円(税込) / Lパック：WEB限定割引49,800円(税込) / LLパック：WEB限定割引98,800円(税込) / XLパック：要相談</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/otasuke-usagi/</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/otasukeusagi.png</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>お助けうさぎの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>2件</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
+          <t>ゴミ屋敷片付け・不用品回収・遺品整理まで幅広く対応可能 / 不用品買取査定により回収費用の軽減が可能 / 関東エリア対応・無料見積りで相談しやすいサービス体制</t>
         </is>
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>不用品回収・ゴミ屋敷片付け・遺品整理・ハウスクリーニングなど、住まいの片付け全般に対応する整理サービス。 家具や家電、生活ゴミなど幅広い不用品の回収・仕分け・搬出を行い、ゴミ屋敷や汚部屋の片付けにも対応します。 さらに不用品の買取査定や清掃作業まで対応し、片付けから住環境の改善まで総合的にサポート。 関東エリアを中心に迅速な対応体制を整えており、見積り無料で相談できる点も特徴です。</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
         <is>
-          <t>https://www.freshman-s.com/</t>
+          <t>https://otasukeusagi.jp/</t>
         </is>
       </c>
     </row>
@@ -33131,154 +33039,106 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>company-2133</t>
+          <t>company-33416</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>エコスポット</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/eco-spot-fuyouhin/</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/eco-spot.png</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>片付け侍</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>エコスポット</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>4.57 （ 7 件 ）</t>
+          <t>（ 0 件 ）</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>不用品回収・ゴミ屋敷片付け・家財整理などに対応する片付けサービス。 家具・家電・生活用品・ゴミ袋など幅広い不用品の回収に対応し、分別不要でまとめて回収できる点が特徴です。 搬出作業はスタッフがすべて行い、狭い通路や運び出しが難しい現場にも対応。即日回収や年中無休の受付体制を整えており、電話・メール・LINEによる無料相談や出張見積りにも対応しています。</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 福岡県</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
-        </is>
-      </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>片付け侍の最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>29歳・男性</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="R214" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応3.5）</t>
-        </is>
-      </c>
+          <t>SSパック：WEB限定割引5,000円(税込) / Sパック：WEB限定割引10,000円(税込) / Mパック：WEB限定割引20,000円(税込) / Lパック：WEB限定割引50,000円(税込) / LLパック：WEB限定割引100,000円(税込) / ゴミ屋敷片付けパック：要相談</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr">
         <is>
-          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
+          <t>現在口コミは投稿されていません</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/eco-spot-fuyouhin/</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/eco-spot.png</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>片付け侍の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
-      </c>
+          <t>エコスポットの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>7件</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+          <t>不用品回収・ゴミ屋敷片付けなど幅広い片付けに対応可能 / 分別不要でまとめて回収できる回収サービス / 年中無休・即日回収対応の柔軟な受付体制</t>
         </is>
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>https://katazuke-s.com/</t>
-        </is>
-      </c>
+          <t>不用品回収・ゴミ屋敷片付け・家財整理などに対応する片付けサービス。 家具・家電・生活用品・ゴミ袋など幅広い不用品の回収に対応し、分別不要でまとめて回収できる点が特徴です。 搬出作業はスタッフがすべて行い、狭い通路や運び出しが難しい現場にも対応。即日回収や年中無休の受付体制を整えており、電話・メール・LINEによる無料相談や出張見積りにも対応しています。</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -33289,152 +33149,152 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>company-4087</t>
+          <t>company-428</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>3.91 （ 6 件 ）</t>
+          <t>4.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+          <t>不用品整理：要見積もり</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>ECO助っ人の最新の口コミ</t>
+          <t>未来応援隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>57歳・女性</t>
+          <t>20歳・男性</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度3.5・対応3）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>ECO助っ人の評判・口コミ</t>
+          <t>未来応援隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
         </is>
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>https://eco-suketto.jp/</t>
+          <t>https://www.miraiouentai.com/</t>
         </is>
       </c>
     </row>
@@ -33447,72 +33307,72 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>company-380</t>
+          <t>company-632</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>3.87 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>東京都 / 神奈川県</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の最新の口コミ</t>
+          <t>フレッシュマンサービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>63歳・女性</t>
+          <t>70代・女性</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -33522,12 +33382,12 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -33537,62 +33397,62 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の評判・口コミ</t>
+          <t>フレッシュマンサービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
         </is>
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>https://koyorecycle.com/</t>
+          <t>https://www.freshman-s.com/</t>
         </is>
       </c>
     </row>
@@ -33605,37 +33465,37 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>company-6234</t>
+          <t>company-2133</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>4.42 （ 7 件 ）</t>
+          <t>4.57 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -33645,47 +33505,47 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの最新の口コミ</t>
+          <t>片付け侍の最新の口コミ</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>40代 男性</t>
+          <t>29歳・男性</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度5・対応3.5）</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -33695,27 +33555,27 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの評判・口コミ</t>
+          <t>片付け侍の評判・口コミ</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
@@ -33725,32 +33585,32 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>https://otasuke-master.co.jp/</t>
+          <t>https://katazuke-s.com/</t>
         </is>
       </c>
     </row>
@@ -33763,87 +33623,87 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>company-8102</t>
+          <t>company-4087</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>3.91 （ 6 件 ）</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>片付け堂の最新の口コミ</t>
+          <t>ECO助っ人の最新の口コミ</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>57歳・女性</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度3.5・対応3）</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
@@ -33853,62 +33713,62 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>片付け堂の評判・口コミ</t>
+          <t>ECO助っ人の評判・口コミ</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
         </is>
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>https://www.katazukedou.com/</t>
+          <t>https://eco-suketto.jp/</t>
         </is>
       </c>
     </row>
@@ -33921,72 +33781,72 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>company-3871</t>
+          <t>company-380</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>5 （ 3 件 ）</t>
+          <t>3.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>福島片付け110番の最新の口コミ</t>
+          <t>紅葉リサイクル福岡の最新の口コミ</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>40代・男性</t>
+          <t>63歳・女性</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -33996,77 +33856,77 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>福島片付け110番の評判・口コミ</t>
+          <t>紅葉リサイクル福岡の評判・口コミ</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
         </is>
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>https://fukushima-kataduke110ban.com/</t>
+          <t>https://koyorecycle.com/</t>
         </is>
       </c>
     </row>
@@ -34079,152 +33939,152 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>company-3850</t>
+          <t>company-6234</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>4.42 （ 7 件 ）</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>40代 男性</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>4.5 （ 4 件 ）</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>福島県 / 茨城県</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>フロンティアグループの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P220" t="inlineStr">
-        <is>
-          <t>30歳・男性</t>
-        </is>
-      </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度4・対応4）</t>
-        </is>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
-        </is>
-      </c>
-      <c r="T220" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>フロンティアグループの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
+      <c r="AB220" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="Y220" t="inlineStr">
+      <c r="AC220" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
         </is>
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
         <is>
-          <t>https://iwaki-benriya.com/</t>
+          <t>https://otasuke-master.co.jp/</t>
         </is>
       </c>
     </row>
@@ -34237,152 +34097,152 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>company-615</t>
+          <t>company-8102</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>5 （ 2 件 ）</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>片付け堂の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>片付け堂の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>4.75 （ 4 件 ）</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
-        </is>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>エコスピードの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>30代 女性</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
-        </is>
-      </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>エコスピードの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
         <is>
-          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
         </is>
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>https://eco-speed.life/</t>
+          <t>https://www.katazukedou.com/</t>
         </is>
       </c>
     </row>
@@ -34395,27 +34255,27 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>company-3839</t>
+          <t>company-3871</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -34425,22 +34285,22 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>5 （ 3 件 ）</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -34450,17 +34310,17 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の最新の口コミ</t>
+          <t>福島片付け110番の最新の口コミ</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>40代・男性</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -34470,32 +34330,32 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の評判・口コミ</t>
+          <t>福島片付け110番の評判・口コミ</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
@@ -34510,12 +34370,12 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
@@ -34530,17 +34390,17 @@
       </c>
       <c r="AD222" t="inlineStr">
         <is>
-          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
         </is>
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
         <is>
-          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+          <t>https://fukushima-kataduke110ban.com/</t>
         </is>
       </c>
     </row>
@@ -34553,150 +34413,624 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
+          <t>company-3850</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>4.5 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>福島県 / 茨城県</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>フロンティアグループの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>30歳・男性</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度4・対応4）</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>フロンティアグループの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>https://iwaki-benriya.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>15</v>
+      </c>
+      <c r="B224" t="n">
+        <v>13</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>company-615</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>4.75 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>エコスピードの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>30代 女性</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>エコスピードの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>https://eco-speed.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>15</v>
+      </c>
+      <c r="B225" t="n">
+        <v>14</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>company-3839</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>5 （ 1 件 ）</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>15</v>
+      </c>
+      <c r="B226" t="n">
+        <v>15</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
           <t>company-418</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G226" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
         <is>
           <t>5 （ 2 件 ）</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr">
+      <c r="J226" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="K226" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t>深夜・早朝の回収 / 即日対応 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t>福岡県 / 長崎県</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr">
+      <c r="N226" t="inlineStr">
         <is>
           <t>単品回収：1点1,000円より</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr">
+      <c r="O226" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の最新の口コミ</t>
         </is>
       </c>
-      <c r="P223" t="inlineStr">
+      <c r="P226" t="inlineStr">
         <is>
           <t>59歳・女性</t>
         </is>
       </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr">
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
         <is>
           <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
-      <c r="S223" t="inlineStr">
+      <c r="S226" t="inlineStr">
         <is>
           <t>問い合わせの迅速な対応。当日も親切に対応していただきました。また機会があれば利用したいと思います。ありがとうございました。</t>
         </is>
       </c>
-      <c r="T223" t="inlineStr">
+      <c r="T226" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="U226" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="V223" t="inlineStr">
+      <c r="V226" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="W223" t="inlineStr">
+      <c r="W226" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の評判・口コミ</t>
         </is>
       </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
         <is>
           <t>2件</t>
         </is>
       </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
         <is>
           <t>1点から不用品を回収してもらえる / 引越しとセットで依頼するとお得 / LINEでスピード見積もりに対応</t>
         </is>
       </c>
-      <c r="AE223" t="inlineStr">
+      <c r="AE226" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="AF223" t="inlineStr"/>
+      <c r="AF226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF226"/>
+  <dimension ref="A1:AF235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>http://www.tglv-kawasaki.com/</t>
+          <t>https://www.tglv-kawasaki.com/</t>
         </is>
       </c>
     </row>
@@ -32838,15 +32838,19 @@
           <t>伊豆クリーン</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>（ 0 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -32865,16 +32869,36 @@
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>伊豆クリーンの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>50代・女性</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度4・対応5）</t>
+        </is>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>現在口コミは投稿されていません</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr"/>
+          <t>実家の片付けで不要になった家具を回収してもらいました。大きなタンスや棚も丁寧に運び出してくれて助かりました。対応も落ち着いていて安心できました。</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/izu-clean-gyosya/</t>
@@ -32890,16 +32914,36 @@
           <t>伊豆クリーンの評判・口コミ</t>
         </is>
       </c>
-      <c r="X212" t="inlineStr"/>
-      <c r="Y212" t="inlineStr"/>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA212" t="inlineStr"/>
-      <c r="AB212" t="inlineStr"/>
-      <c r="AC212" t="inlineStr"/>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD212" t="inlineStr">
         <is>
           <t>ゴミ屋敷片付け・不用品回収・遺品整理など幅広い片付けに対応可能 / 未分別のゴミでも仕分けから搬出まで対応可能 / 不用品の買取査定により回収費用の軽減が可能</t>
@@ -32948,15 +32992,19 @@
           <t>お助けうさぎ</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>（ 0 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -32979,16 +33027,36 @@
           <t>SSパック：WEB限定割引4,980円(税込) / Sパック：WEB限定割引12,800円(税込) / Mパック：WEB限定割引29,800円(税込) / Lパック：WEB限定割引49,800円(税込) / LLパック：WEB限定割引98,800円(税込) / XLパック：要相談</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>お助けうさぎの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>30代・女性</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>現在口コミは投稿されていません</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr"/>
+          <t>家電の買い替えで古いものを処分する必要があり依頼しました。スタッフの方が手際よく運び出してくれて安心しました。部屋もすっきりして気持ちよく新生活を始められます。</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
       <c r="U213" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/otasuke-usagi/</t>
@@ -33004,16 +33072,36 @@
           <t>お助けうさぎの評判・口コミ</t>
         </is>
       </c>
-      <c r="X213" t="inlineStr"/>
-      <c r="Y213" t="inlineStr"/>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr"/>
-      <c r="AB213" t="inlineStr"/>
-      <c r="AC213" t="inlineStr"/>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD213" t="inlineStr">
         <is>
           <t>ゴミ屋敷片付け・不用品回収・遺品整理まで幅広く対応可能 / 不用品買取査定により回収費用の軽減が可能 / 関東エリア対応・無料見積りで相談しやすいサービス体制</t>
@@ -33062,15 +33150,19 @@
           <t>エコスポット</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>（ 0 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -33093,16 +33185,36 @@
           <t>SSパック：WEB限定割引5,000円(税込) / Sパック：WEB限定割引10,000円(税込) / Mパック：WEB限定割引20,000円(税込) / Lパック：WEB限定割引50,000円(税込) / LLパック：WEB限定割引100,000円(税込) / ゴミ屋敷片付けパック：要相談</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>エコスポットの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>20代・女性</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度4・対応5）</t>
+        </is>
+      </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>現在口コミは投稿されていません</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr"/>
+          <t>退去日が迫っていて焦っていましたが、すぐに対応してくれました。作業も丁寧で部屋を傷つけることなく運び出してくれました。</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
       <c r="U214" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/eco-spot-fuyouhin/</t>
@@ -33118,16 +33230,36 @@
           <t>エコスポットの評判・口コミ</t>
         </is>
       </c>
-      <c r="X214" t="inlineStr"/>
-      <c r="Y214" t="inlineStr"/>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr"/>
-      <c r="AB214" t="inlineStr"/>
-      <c r="AC214" t="inlineStr"/>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD214" t="inlineStr">
         <is>
           <t>不用品回収・ゴミ屋敷片付けなど幅広い片付けに対応可能 / 分別不要でまとめて回収できる回収サービス / 年中無休・即日回収対応の柔軟な受付体制</t>
@@ -33149,52 +33281,52 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>company-428</t>
+          <t>company-33419</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>喜ばせ隊</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/fuyouhin-yorokobasetai/</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/yorokobasetai.png</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>喜ばせ隊</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>4.87 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>不用品回収・ゴミ屋敷片付け・汚部屋整理・遺品整理・生前整理など住まいの片付け全般をサポートする整理・片付けサービスです。 家具・家電・生活ゴミなど幅広い不用品の仕分け・搬出・処分に対応し、混在状態でもスタッフが丁寧に対応。 ハウスクリーニングや消臭・除菌などの清掃作業も行い、片付け後の住環境改善まで支援します。出張見積りで費用を事前に確認できる点が特徴です。</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 買取対応 / 単品回収可能</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -33202,79 +33334,75 @@
           <t>静岡県</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>不用品整理：要見積もり</t>
-        </is>
-      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
-          <t>未来応援隊の最新の口コミ</t>
+          <t>喜ばせ隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>20歳・男性</t>
+          <t>30代・女性</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
+          <t>自分では動かせない家具があり依頼しました。養生もきちんとしてくれて、安心して見ていられました。お願いしてよかったです。</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/fuyouhin-yorokobasetai/</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/yorokobasetai.png</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>未来応援隊の評判・口コミ</t>
+          <t>喜ばせ隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
@@ -33284,17 +33412,17 @@
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
+          <t>不用品回収・ゴミ屋敷片付け・遺品整理まで幅広く対応可能 / 生活ゴミや混在ゴミの仕分け・搬出・清掃まで一貫対応可能 / 出張見積りによる料金の事前確認ができる体制</t>
         </is>
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>不用品回収・ゴミ屋敷片付け・汚部屋整理・遺品整理・生前整理など住まいの片付け全般をサポートする整理・片付けサービスです。 家具・家電・生活ゴミなど幅広い不用品の仕分け・搬出・処分に対応し、混在状態でもスタッフが丁寧に対応。 ハウスクリーニングや消臭・除菌などの清掃作業も行い、片付け後の住環境改善まで支援します。出張見積りで費用を事前に確認できる点が特徴です。</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>https://www.miraiouentai.com/</t>
+          <t>https://www.yorokobasetai.com/</t>
         </is>
       </c>
     </row>
@@ -33307,27 +33435,27 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>company-632</t>
+          <t>company-33422</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>再生市場</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/saisei-ichiba-fuyouhin/</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/saisei-ichiba.png</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>再生市場</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -33347,32 +33475,28 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>家具・家電・生活用品などの不要品の仕分け・搬出・処分に対応し、混在したゴミの整理や片付けを効率的に行います。 また、買取査定にも対応しており、不要品の買取を通じて回収費用の軽減につなげられる点が特徴です。 出張見積りや相談無料で、依頼者の希望やスケジュールに沿った柔軟なサービス提供を行っています。</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>東京都 / 神奈川県</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
-        </is>
-      </c>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの最新の口コミ</t>
+          <t>再生市場の最新の口コミ</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>70代・女性</t>
+          <t>50代・男性</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -33382,32 +33506,32 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
+          <t>新しい家具を購入したため古いものを回収してもらいました。スタッフの方が丁寧に搬出してくれて安心しました。</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/saisei-ichiba-fuyouhin/</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/saisei-ichiba.png</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの評判・口コミ</t>
+          <t>再生市場の評判・口コミ</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
@@ -33432,7 +33556,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
@@ -33442,17 +33566,17 @@
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
+          <t>ゴミ屋敷片付け・不用品回収・遺品整理まで幅広く対応可能 / 不用品買取査定による費用軽減につなげられる体制 / 出張見積り・無料相談による安心感</t>
         </is>
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>家具・家電・生活用品などの不要品の仕分け・搬出・処分に対応し、混在したゴミの整理や片付けを効率的に行います。 また、買取査定にも対応しており、不要品の買取を通じて回収費用の軽減につなげられる点が特徴です。 出張見積りや相談無料で、依頼者の希望やスケジュールに沿った柔軟なサービス提供を行っています。</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>https://www.freshman-s.com/</t>
+          <t>https://www.saisei-ichiba.com/index.html</t>
         </is>
       </c>
     </row>
@@ -33465,152 +33589,152 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>company-2133</t>
+          <t>company-33425</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>エコクリーンラボ</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/eco-cleanlabo-fuyouhin/</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/eco-cleanlabo.png</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>エコクリーンラボ</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>4.57 （ 7 件 ）</t>
+          <t>5 （ 1 件 ）</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>静岡県を中心に不用品回収・ゴミ屋敷片付け・整理全般を手がける片付けサービス。 家具・家電・生活ゴミなどの不要品を仕分け・搬出・処分し、混在ゴミのまとめ回収にも対応します。 また遺品整理・生前整理や引越しに伴う片付けまでカバー。出張見積り・相談無料で、現地状況に合わせた最適なプラン提案を行い、生活環境の改善をサポートする点が特徴です。</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>神奈川県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 三重県</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
+          <t>プチパック：Web割 5,000円(税込)〜 / Sパック：Web割 9,000円(税込)〜 / Mパック：Web割 20,000円(税込)〜 / LLパック：要相談 / 家一棟お片付けパック：要相談</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>片付け侍の最新の口コミ</t>
+          <t>エコクリーンラボの最新の口コミ</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>29歳・男性</t>
+          <t>40代・女性</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応3.5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
+          <t>初めて利用しましたが、見積りから回収まで丁寧でした。大型家具も問題なく回収してもらえました。</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/eco-cleanlabo-fuyouhin/</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/eco-cleanlabo.png</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>片付け侍の評判・口コミ</t>
+          <t>エコクリーンラボの評判・口コミ</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+          <t>ゴミ屋敷片付け・不用品回収・整理全般に対応可能 / 混在ゴミの仕分け・搬出・処分まで一貫対応可能 / 出張見積り・相談無料で状況に合わせたプラン提案</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>静岡県を中心に不用品回収・ゴミ屋敷片付け・整理全般を手がける片付けサービス。 家具・家電・生活ゴミなどの不要品を仕分け・搬出・処分し、混在ゴミのまとめ回収にも対応します。 また遺品整理・生前整理や引越しに伴う片付けまでカバー。出張見積り・相談無料で、現地状況に合わせた最適なプラン提案を行い、生活環境の改善をサポートする点が特徴です。</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>https://katazuke-s.com/</t>
+          <t>https://eco-cleanlabo.com/</t>
         </is>
       </c>
     </row>
@@ -33623,152 +33747,152 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>company-4087</t>
+          <t>company-33429</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>エコピット</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/ecopit-huyouhin/</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/ecopit-huyouhin.png</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>エコピット</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>3.91 （ 6 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>家具・家電・生活用品など幅広い不要品の整理を手がける片付けサービスです。 仕分け・搬出・処分に対応し、分別が難しい混在ゴミの回収にも対応。 引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適プランを提案します。 地域密着の迅速対応で、忙しい方の負担を軽減する点が特徴です。</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>東京都 / 神奈川県 / 千葉県</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+          <t>SSパック：9,900円〜 / 軽トラックパック|Sパック：19,800円〜 / 平トラックパック|Mパック：34,800円〜 / 2tトラックパック｜Lパック：69,800円〜</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>ECO助っ人の最新の口コミ</t>
+          <t>エコピットの最新の口コミ</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>57歳・女性</t>
+          <t>30代・男性</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度3.5・対応3）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+          <t>細かい家具や家電を一度に回収してもらいました。分別や搬出も手際が良く、安心できました。</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/ecopit-huyouhin/</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/ecopit-huyouhin.png</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>ECO助っ人の評判・口コミ</t>
+          <t>エコピットの評判・口コミ</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+          <t>ゴミ屋敷片付け・不用品回収・粗大ごみ処分まで幅広く対応可能 / 混在ゴミの仕分け・搬出・処分まで一貫対応可能 / 出張見積り・相談無料で状況に合わせたプラン提案</t>
         </is>
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>家具・家電・生活用品など幅広い不要品の整理を手がける片付けサービスです。 仕分け・搬出・処分に対応し、分別が難しい混在ゴミの回収にも対応。 引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適プランを提案します。 地域密着の迅速対応で、忙しい方の負担を軽減する点が特徴です。</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>https://eco-suketto.jp/</t>
+          <t>https://www.ecopit-huyouhin.com/</t>
         </is>
       </c>
     </row>
@@ -33781,72 +33905,72 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>company-380</t>
+          <t>company-33432</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>ワンナップLIFE</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/one-up-life-gyosya/</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/one-up-life.png</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>ワンナップLIFE</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>3.87 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>家具・家電・生活用品などの不要品の仕分け・搬出・処分に対応し、混在ゴミ・大量ゴミの整理も柔軟に対応。 さらにハウスクリーニング・清掃・消臭など住環境の改善作業も行い、生活の負担を軽減します。 出張見積り・相談無料で、依頼者の希望に合わせたプラン提案による柔軟な対応が特徴です。</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>東京都 / 埼玉県 / 神奈川県 / 千葉県</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+          <t>Sパック：割引適用 9,800円～税込 / Mパック：割引適用 34,800円～税込 / Lパック：割引適用 54,800円～税込 / LLパック：要相談</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の最新の口コミ</t>
+          <t>ワンナップLIFEの最新の口コミ</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>63歳・女性</t>
+          <t>50代・男性</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -33861,72 +33985,72 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+          <t>片付けられずにいた部屋がどんどん物で埋もれてしまい、自分ではどうにもできない状態でした。依頼するとスタッフの方が丁寧に対応してくれて安心しました。分別しながら作業してくれて、部屋がかなりきれいになりました。</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/one-up-life-gyosya/</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/one-up-life.png</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の評判・口コミ</t>
+          <t>ワンナップLIFEの評判・口コミ</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+          <t>ゴミ屋敷片付け・不用品回収・整理全般に対応可能 / 生活ゴミや混在ゴミの仕分け・搬出・清掃まで一貫対応可能 / 出張見積り・相談無料で柔軟なプラン提案による安心感</t>
         </is>
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>家具・家電・生活用品などの不要品の仕分け・搬出・処分に対応し、混在ゴミ・大量ゴミの整理も柔軟に対応。 さらにハウスクリーニング・清掃・消臭など住環境の改善作業も行い、生活の負担を軽減します。 出張見積り・相談無料で、依頼者の希望に合わせたプラン提案による柔軟な対応が特徴です。</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>https://koyorecycle.com/</t>
+          <t>https://one-up-life.com/</t>
         </is>
       </c>
     </row>
@@ -33939,72 +34063,68 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>company-6234</t>
+          <t>company-33435</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>すぐ片付け隊</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/fuyouhin-sugukataduketai-gyosya/</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/fuyouhin-sugukataduketai.png</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>すぐ片付け隊</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>4.42 （ 7 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>東京都 / 埼玉県 / 神奈川県 / 千葉県</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+          <t>Sプラン：11,000円（税込）～ / Mプラン：14,300円（税込）～ / Lプラン：22,000円（税込）～ / LLプラン：44,000円（税込）～ / XLプラン：110,000円（税込）～</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの最新の口コミ</t>
+          <t>すぐ片付け隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>40代 男性</t>
+          <t>40代・女性</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -34014,77 +34134,69 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+          <t>長い間処分できなかった家具があり困っていましたが、依頼して本当に正解でした。スタッフの方が丁寧に対応してくれて、短時間で部屋が整いました。</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/fuyouhin-sugukataduketai-gyosya/</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/fuyouhin-sugukataduketai.png</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの評判・口コミ</t>
+          <t>すぐ片付け隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr"/>
+      <c r="AE220" t="inlineStr"/>
       <c r="AF220" t="inlineStr">
         <is>
-          <t>https://otasuke-master.co.jp/</t>
+          <t>https://fuyouhin-sugukataduketai.com/</t>
         </is>
       </c>
     </row>
@@ -34097,27 +34209,27 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>company-8102</t>
+          <t>company-33438</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>ごみ怪獣</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/gomi-kaiju-gyosya/</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/gomi-kaiju.png</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>ごみ怪獣</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -34137,32 +34249,32 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>不用品回収・ゴミ屋敷片付け・整理サービス全般を手がける片付け業者です。 家具・家電・生活ゴミ・混在ゴミなど幅広い不要品の仕分け・搬出・処分に対応し、分別が難しい状態でもスタッフが丁寧に片付けます。 また、引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適なプラン提案を行う点が特徴です。</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+          <t>東京都 / 埼玉県 / 神奈川県 / 千葉県</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+          <t>SSプラン：WEB限定割引 4,000~円(税込) / Sプラン：WEB限定割引 10,000~円(税込) / Mプラン：WEB限定割引 20,000~円(税込) / Lプラン：50,000~円(税込) / LLプラン：100,000~円(税込) / 3Lプラン：要相談</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>片付け堂の最新の口コミ</t>
+          <t>ごみ怪獣の最新の口コミ</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>40代・男性</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -34177,27 +34289,27 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+          <t>処分方法が分からなかった大型家具を回収してもらいました。スタッフの方が丁寧で安心して任せることができました。</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/gomi-kaiju-gyosya/</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/gomi-kaiju.png</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>片付け堂の評判・口コミ</t>
+          <t>ごみ怪獣の評判・口コミ</t>
         </is>
       </c>
       <c r="X221" t="inlineStr">
@@ -34222,7 +34334,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
@@ -34232,17 +34344,17 @@
       </c>
       <c r="AD221" t="inlineStr">
         <is>
-          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+          <t>不用品回収・ゴミ屋敷片付け・整理全般に対応可能 / 生活ゴミ・混在ゴミの仕分け・搬出・処分まで一貫対応可能 / 出張見積り・相談無料で柔軟なプラン提案による安心感</t>
         </is>
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>不用品回収・ゴミ屋敷片付け・整理サービス全般を手がける片付け業者です。 家具・家電・生活ゴミ・混在ゴミなど幅広い不要品の仕分け・搬出・処分に対応し、分別が難しい状態でもスタッフが丁寧に片付けます。 また、引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適なプラン提案を行う点が特徴です。</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>https://www.katazukedou.com/</t>
+          <t>https://gomi-kaiju.com/</t>
         </is>
       </c>
     </row>
@@ -34255,27 +34367,27 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>company-3871</t>
+          <t>company-33441</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>不用品回収ダッシュ世田谷</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/dash-tokyo/</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/dash.tokyo_.png</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>不用品回収ダッシュ世田谷</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -34285,42 +34397,38 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>5 （ 3 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>不用品回収・ゴミ屋敷片付け・整理サービス全般を手がける片付け業者です。 家具・家電・生活ゴミ・混在ゴミなど幅広い不要品の仕分け・搬出・処分に対応し、分別が難しい状態でもスタッフが丁寧に片付けます。 また、引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適なプラン提案を行う点が特徴です。</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>福島県</t>
-        </is>
-      </c>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
         <is>
-          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+          <t>軽トラパック：19,500円 / 1.5tパック：35,000円 / 2tパック：49,800円</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>福島片付け110番の最新の口コミ</t>
+          <t>不用品回収ダッシュ世田谷の最新の口コミ</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>40代・男性</t>
+          <t>40代・女性</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -34330,32 +34438,32 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+          <t>不要品を回収してもらった後の部屋がとても広く感じられました。対応も丁寧で安心できました。</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/dash-tokyo/</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/dash.tokyo_.png</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>福島片付け110番の評判・口コミ</t>
+          <t>不用品回収ダッシュ世田谷の評判・口コミ</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
@@ -34370,17 +34478,17 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
@@ -34390,17 +34498,17 @@
       </c>
       <c r="AD222" t="inlineStr">
         <is>
-          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+          <t>不用品回収・ゴミ屋敷片付け・整理全般に対応可能 / 生活ゴミ・混在ゴミの仕分け・搬出・処分まで一貫対応可能 / 出張見積り・相談無料で柔軟なプラン提案による安心感</t>
         </is>
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>不用品回収・ゴミ屋敷片付け・整理サービス全般を手がける片付け業者です。 家具・家電・生活ゴミ・混在ゴミなど幅広い不要品の仕分け・搬出・処分に対応し、分別が難しい状態でもスタッフが丁寧に片付けます。 また、引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適なプラン提案を行う点が特徴です。</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
         <is>
-          <t>https://fukushima-kataduke110ban.com/</t>
+          <t>https://dash.tokyo/</t>
         </is>
       </c>
     </row>
@@ -34413,152 +34521,144 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>company-3850</t>
+          <t>company-33444</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>有限会社和田</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/wada-atami-fuyouhin/</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/wada-atami.png</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>有限会社和田</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>5 （ 2 件 ）</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>静岡県熱海市を中心にゴミ屋敷片付け・不用品回収・整理全般をサポートする片付けサービスです。 生活ゴミや混在した不用品の仕分け・搬出・処分に対応し、家具・家電の回収も柔軟に行います。 出張見積り・相談無料で、依頼者のニーズに合わせたプラン提案を行う点が特徴です。</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>有限会社和田の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>30代・女性</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度4・対応5）</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>部屋に置いたままだった家具を一掃できました。スタッフの方の対応も良く、安心して任せられました。</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wada-atami-fuyouhin/</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/wada-atami.png</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>有限会社和田の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>4.5 （ 4 件 ）</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>福島県 / 茨城県</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
-        </is>
-      </c>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>フロンティアグループの最新の口コミ</t>
-        </is>
-      </c>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>30歳・男性</t>
-        </is>
-      </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr">
-        <is>
-          <t>（回収料金4・回収速度4・対応4）</t>
-        </is>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
-        </is>
-      </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>フロンティアグループの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
         <is>
-          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+          <t>ゴミ屋敷片付け・不用品回収・整理全般に対応可能 / 生活ゴミ・混在ゴミの仕分け・搬出・処分まで一貫対応可能 / 遺品整理・掃除・消臭など住環境改善まで対応可能</t>
         </is>
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>静岡県熱海市を中心にゴミ屋敷片付け・不用品回収・整理全般をサポートする片付けサービスです。 生活ゴミや混在した不用品の仕分け・搬出・処分に対応し、家具・家電の回収も柔軟に行います。 出張見積り・相談無料で、依頼者のニーズに合わせたプラン提案を行う点が特徴です。</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
         <is>
-          <t>https://iwaki-benriya.com/</t>
+          <t>https://www.wada-atami.com/</t>
         </is>
       </c>
     </row>
@@ -34571,27 +34671,27 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>company-615</t>
+          <t>company-428</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -34601,7 +34701,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>4.75 （ 4 件 ）</t>
+          <t>4.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -34611,67 +34711,67 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+          <t>不用品整理：要見積もり</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>エコスピードの最新の口コミ</t>
+          <t>未来応援隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>30代 女性</t>
+          <t>20歳・男性</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>エコスピードの評判・口コミ</t>
+          <t>未来応援隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
@@ -34681,19 +34781,19 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
           <t>4.75</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>4件</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
       <c r="AB224" t="inlineStr">
         <is>
           <t>4.75</t>
@@ -34701,22 +34801,22 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
         <is>
-          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
         </is>
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
         <is>
-          <t>https://eco-speed.life/</t>
+          <t>https://www.miraiouentai.com/</t>
         </is>
       </c>
     </row>
@@ -34729,27 +34829,27 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>company-3839</t>
+          <t>company-632</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -34759,42 +34859,42 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>東京都 / 神奈川県</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の最新の口コミ</t>
+          <t>フレッシュマンサービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>70代・女性</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -34809,7 +34909,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -34819,17 +34919,17 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の評判・口コミ</t>
+          <t>フレッシュマンサービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
@@ -34844,7 +34944,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -34864,17 +34964,17 @@
       </c>
       <c r="AD225" t="inlineStr">
         <is>
-          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
         </is>
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+          <t>https://www.freshman-s.com/</t>
         </is>
       </c>
     </row>
@@ -34887,150 +34987,1572 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
+          <t>company-2133</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>片付け侍</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>片付け侍</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>4.57 （ 7 件 ）</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>片付け侍の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>29歳・男性</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応3.5）</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>片付け侍の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>https://katazuke-s.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>16</v>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>company-4087</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ECO助っ人</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>ECO助っ人</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>3.91 （ 6 件 ）</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>ECO助っ人の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>57歳・女性</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度3.5・対応3）</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>ECO助っ人の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>https://eco-suketto.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>16</v>
+      </c>
+      <c r="B228" t="n">
+        <v>2</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>company-380</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>3.87 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>63歳・女性</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度4・対応5）</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>https://koyorecycle.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>16</v>
+      </c>
+      <c r="B229" t="n">
+        <v>3</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>company-6234</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスター</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスター</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>4.42 （ 7 件 ）</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>40代 男性</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>便利屋お助けマスターの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>https://otasuke-master.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>16</v>
+      </c>
+      <c r="B230" t="n">
+        <v>4</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>company-8102</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>片付け堂</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>片付け堂</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>5 （ 2 件 ）</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>片付け堂の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>片付け堂の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>https://www.katazukedou.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>16</v>
+      </c>
+      <c r="B231" t="n">
+        <v>5</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>company-3871</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>福島片付け110番</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>福島片付け110番</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>5 （ 3 件 ）</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>福島片付け110番の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>40代・男性</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>福島片付け110番の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>https://fukushima-kataduke110ban.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>16</v>
+      </c>
+      <c r="B232" t="n">
+        <v>6</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>company-3850</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>フロンティアグループ</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>4.5 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>福島県 / 茨城県</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>フロンティアグループの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>30歳・男性</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>（回収料金4・回収速度4・対応4）</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>フロンティアグループの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>https://iwaki-benriya.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>16</v>
+      </c>
+      <c r="B233" t="n">
+        <v>7</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>company-615</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>エコスピード</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>4.75 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>エコスピードの最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>30代 女性</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>エコスピードの評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>https://eco-speed.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>16</v>
+      </c>
+      <c r="B234" t="n">
+        <v>8</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>company-3839</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>5 （ 1 件 ）</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>16</v>
+      </c>
+      <c r="B235" t="n">
+        <v>9</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
           <t>company-418</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
         <is>
           <t>5 （ 2 件 ）</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr">
+      <c r="J235" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="K235" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t>深夜・早朝の回収 / 即日対応 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t>福岡県 / 長崎県</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
+      <c r="N235" t="inlineStr">
         <is>
           <t>単品回収：1点1,000円より</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr">
+      <c r="O235" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の最新の口コミ</t>
         </is>
       </c>
-      <c r="P226" t="inlineStr">
+      <c r="P235" t="inlineStr">
         <is>
           <t>59歳・女性</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R226" t="inlineStr">
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
         <is>
           <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
-      <c r="S226" t="inlineStr">
+      <c r="S235" t="inlineStr">
         <is>
           <t>問い合わせの迅速な対応。当日も親切に対応していただきました。また機会があれば利用したいと思います。ありがとうございました。</t>
         </is>
       </c>
-      <c r="T226" t="inlineStr">
+      <c r="T235" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="U235" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="V226" t="inlineStr">
+      <c r="V235" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="W226" t="inlineStr">
+      <c r="W235" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の評判・口コミ</t>
         </is>
       </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
         <is>
           <t>2件</t>
         </is>
       </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr">
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
         <is>
           <t>1点から不用品を回収してもらえる / 引越しとセットで依頼するとお得 / LINEでスピード見積もりに対応</t>
         </is>
       </c>
-      <c r="AE226" t="inlineStr">
+      <c r="AE235" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="AF226" t="inlineStr"/>
+      <c r="AF235" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF235"/>
+  <dimension ref="A1:AF236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33840,61 +33840,17 @@
           <t>https://fuyouhincenter.jp/ecopit-huyouhin/</t>
         </is>
       </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/ecopit-huyouhin.png</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>エコピットの評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>2件</t>
-        </is>
-      </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>ゴミ屋敷片付け・不用品回収・粗大ごみ処分まで幅広く対応可能 / 混在ゴミの仕分け・搬出・処分まで一貫対応可能 / 出張見積り・相談無料で状況に合わせたプラン提案</t>
-        </is>
-      </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>家具・家電・生活用品など幅広い不要品の整理を手がける片付けサービスです。 仕分け・搬出・処分に対応し、分別が難しい混在ゴミの回収にも対応。 引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適プランを提案します。 地域密着の迅速対応で、忙しい方の負担を軽減する点が特徴です。</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>https://www.ecopit-huyouhin.com/</t>
-        </is>
-      </c>
+      <c r="V218" t="inlineStr"/>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="inlineStr"/>
+      <c r="AF218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -34456,61 +34412,17 @@
           <t>https://fuyouhincenter.jp/dash-tokyo/</t>
         </is>
       </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/02/dash.tokyo_.png</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>不用品回収ダッシュ世田谷の評判・口コミ</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>2件</t>
-        </is>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>不用品回収・ゴミ屋敷片付け・整理全般に対応可能 / 生活ゴミ・混在ゴミの仕分け・搬出・処分まで一貫対応可能 / 出張見積り・相談無料で柔軟なプラン提案による安心感</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>不用品回収・ゴミ屋敷片付け・整理サービス全般を手がける片付け業者です。 家具・家電・生活ゴミ・混在ゴミなど幅広い不要品の仕分け・搬出・処分に対応し、分別が難しい状態でもスタッフが丁寧に片付けます。 また、引越しに伴う大量片付けや遺品整理・生前整理など幅広いニーズに応え、出張見積り・相談無料で状況に合わせた最適なプラン提案を行う点が特徴です。</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>https://dash.tokyo/</t>
-        </is>
-      </c>
+      <c r="V222" t="inlineStr"/>
+      <c r="W222" t="inlineStr"/>
+      <c r="X222" t="inlineStr"/>
+      <c r="Y222" t="inlineStr"/>
+      <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="inlineStr"/>
+      <c r="AC222" t="inlineStr"/>
+      <c r="AD222" t="inlineStr"/>
+      <c r="AE222" t="inlineStr"/>
+      <c r="AF222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -34671,132 +34583,132 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>company-428</t>
+          <t>company-34636</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>不用品回収スポット栃木</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/tochigi-fuyouhin-spot/</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/03/tochigi.fuyouhin-center.png</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>未来応援隊</t>
+          <t>不用品回収スポット栃木</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>4.87 （ 4 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>栃木不用品回収センターは、家具・家電から生活用品まで幅広い不用品に対応し、最短当日での回収が可能なスピード対応が強みの業者です。分別不要でそのまま依頼できるため、手間をかけずに片付けを進められます。遺品整理やゴミ屋敷の清掃にも対応しており、経験豊富なスタッフが丁寧に作業を行う点も特徴です。無料見積もりや追加料金なしの明朗会計で、初めてでも利用しやすいサービスとなっています。</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>不用品整理：要見積もり</t>
+          <t>SSパック：4,900円～ / Sパック：9,900円～ / Mパック：18,900円～ / Lパック：30,000円～ / LLパック： / 都度見積もり：都度見積もり</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>未来応援隊の最新の口コミ</t>
+          <t>不用品回収スポット栃木の最新の口コミ</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>20歳・男性</t>
+          <t>50代・女性</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度4・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
+          <t>実家の片付けで利用しました。量が多く不安でしたが、見積もりの段階から分かりやすく説明してくれました。作業も丁寧で、思い出の品についても気遣っていただき感謝しています。スタッフの対応の良さが印象に残りました。</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/miraiouentai/</t>
+          <t>https://fuyouhincenter.jp/tochigi-fuyouhin-spot/</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2026/03/tochigi.fuyouhin-center.png</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>未来応援隊の評判・口コミ</t>
+          <t>不用品回収スポット栃木の評判・口コミ</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -34806,17 +34718,17 @@
       </c>
       <c r="AD224" t="inlineStr">
         <is>
-          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
+          <t>総実績13万件突破 / お客様満足度97％ / 多数メディア掲載</t>
         </is>
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
+          <t>栃木不用品回収センターは、家具・家電から生活用品まで幅広い不用品に対応し、最短当日での回収が可能なスピード対応が強みの業者です。分別不要でそのまま依頼できるため、手間をかけずに片付けを進められます。遺品整理やゴミ屋敷の清掃にも対応しており、経験豊富なスタッフが丁寧に作業を行う点も特徴です。無料見積もりや追加料金なしの明朗会計で、初めてでも利用しやすいサービスとなっています。</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
         <is>
-          <t>https://www.miraiouentai.com/</t>
+          <t>https://tochigi.fuyouhin-center.jp/</t>
         </is>
       </c>
     </row>
@@ -34829,132 +34741,132 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>company-632</t>
+          <t>company-428</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>フレッシュマンサービス</t>
+          <t>未来応援隊</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>4.87 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>東京都 / 神奈川県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
+          <t>不用品整理：要見積もり</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの最新の口コミ</t>
+          <t>未来応援隊の最新の口コミ</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>70代・女性</t>
+          <t>20歳・男性</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
+          <t>未来応援隊にお世話になったんだけど、本当に良かった！スタッフの人たちがめっちゃ感じ良くてビックリ。今まで色んな業者使ってきたけど、ダントツNo.1。 料金もべらぼうに高いわけじゃなくて、むしろ良心的な感じ。ありがたかったなぁ。暑い時期は大変だろうけど、無理しないでほしい。みんなも困ったら未来応援隊、おすすめだよ！</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/freshmanservice/</t>
+          <t>https://fuyouhincenter.jp/miraiouentai/</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/miraiouentai-samune.png</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスの評判・口コミ</t>
+          <t>未来応援隊の評判・口コミ</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
@@ -34964,17 +34876,17 @@
       </c>
       <c r="AD225" t="inlineStr">
         <is>
-          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
+          <t>草刈りや伐採も依頼できる / 寄り添うお手伝いをモットーとした親切な対応 / 相談や見積もりは無料</t>
         </is>
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
+          <t>未来応援隊は不用品回収や遺品整理のサービスを提供しています。 草刈りやゴミ屋敷の片付けも依頼できます。 経験豊富なスタッフが心を込めて対応してくれる地域密着型の業者です。</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>https://www.freshman-s.com/</t>
+          <t>https://www.miraiouentai.com/</t>
         </is>
       </c>
     </row>
@@ -34987,152 +34899,152 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>company-2133</t>
+          <t>company-632</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>片付け侍</t>
+          <t>フレッシュマンサービス</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>4.57 （ 7 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>東京都 / 神奈川県</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
+          <t>出張金額＋プラン（作業料金）：出張料金【移動距離10ｋｍ圏内まで2,200円 ・以降10ｋｍ増加につき2,200円追加】 / 例）不用品リサイクル回収プラン：出張料金10km圏内2,200円（税込）＋作業料金１品/550円～ / 例）お部屋片付け 定額ライトプラン：定額料金 38,500円（税込） / 例）遺品整理・部屋片付けプラン：1LDK・2DK（約８㎥～ ） 88,000円～</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>片付け侍の最新の口コミ</t>
+          <t>フレッシュマンサービスの最新の口コミ</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>29歳・男性</t>
+          <t>70代・女性</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応3.5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
+          <t>日常生活のサポートもしてくれる便利屋フレッシュマンさん！アパートの部屋への重い荷物持ちや部屋も模様替えなど、力仕事はつい頼ってしまいます。いつも助かっています。</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazuke-s/</t>
+          <t>https://fuyouhincenter.jp/freshmanservice/</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-16-150121-1.png</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>片付け侍の評判・口コミ</t>
+          <t>フレッシュマンサービスの評判・口コミ</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
         <is>
-          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
+          <t>不用品回収や遺品整理の他16項目以上の困りごとに対応 / 相談・見積もりが無料 / 引っ越しも対応している</t>
         </is>
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
+          <t>フレッシュマンサービスは、不用品回収から遺品整理、リサイクル、買取など幅広いサービスを提供しています。 リサイクルショップの運営もしていて不用品のリサイクルを特に得意としています。 回収や片付けサービスだけでなく、単身引っ越しも対応している不用品回収業者です。</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
         <is>
-          <t>https://katazuke-s.com/</t>
+          <t>https://www.freshman-s.com/</t>
         </is>
       </c>
     </row>
@@ -35145,152 +35057,152 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>company-4087</t>
+          <t>company-2133</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>ECO助っ人</t>
+          <t>片付け侍</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>3.91 （ 6 件 ）</t>
+          <t>4.57 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 三重県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
+          <t>Sパック：11,880円～ / Mパック：29,700円～ / Lパック：39,600円～ / XLパック：49,500円～</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>ECO助っ人の最新の口コミ</t>
+          <t>片付け侍の最新の口コミ</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>57歳・女性</t>
+          <t>29歳・男性</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度3.5・対応3）</t>
+          <t>（回収料金5・回収速度5・対応3.5）</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
+          <t>担当の方が終始丁寧に接してくださり、とても気持ちよく利用できました。予想よりもずっとリーズナブルな価格設定で、家計に優しいサービスだったのが嬉しかったです。依頼してからの作業スピードも驚くほど速く、急いでいた私にとって本当に助かりました。このような素晴らしいサービスなら、次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecosuketto/</t>
+          <t>https://fuyouhincenter.jp/katazuke-s/</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/07/katazukes.png</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>ECO助っ人の評判・口コミ</t>
+          <t>片付け侍の評判・口コミ</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
+          <t>最短30分で駆けつけて見積もり、即日対応も可能 / 顧客満足度96.3%、信頼できるサービス / クレジットカード、現金、電子マネー、振込</t>
         </is>
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
+          <t>不用品回収・粗大ゴミ回収なら高価買取ありで即日回収の片付け侍は迅速かつ信頼性の高い不用品回収サービスを提供しています。 即日対応可能で、事前見積もり無料、追加費用なし、出張費無料、キャンセル無料などのサービスが特徴です。 また、買取も同時に行い、プライバシー保護や高い顧客満足度を誇っています。 自社の買取ノウハウを生かし、買取おすすめ比較の窓口の運営も行っています。 奈良県の方は、出張買取の窓口｜リサイクルショップが高価買取をご覧ください。</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
         <is>
-          <t>https://eco-suketto.jp/</t>
+          <t>https://katazuke-s.com/</t>
         </is>
       </c>
     </row>
@@ -35303,27 +35215,27 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>company-380</t>
+          <t>company-4087</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡</t>
+          <t>ECO助っ人</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -35333,57 +35245,57 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>3.87 （ 4 件 ）</t>
+          <t>3.91 （ 6 件 ）</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>北海道 / 岩手県 / 宮城県 / 山形県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 山梨県 / 長野県 / 岐阜県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 香川県 / 愛媛県 / 高知県 / 徳島県</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
+          <t>SSパック：5,000円〜 / Sパック：10,000円〜 / Mパック：20,000円〜 / Lパック：50,000円〜 / LLパック：100,000円〜 / 3Lパック：お見積もり・相談</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の最新の口コミ</t>
+          <t>ECO助っ人の最新の口コミ</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>63歳・女性</t>
+          <t>57歳・女性</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度4・対応5）</t>
+          <t>（回収料金4・回収速度3.5・対応3）</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
+          <t>担当者の方がとても丁寧に作業内容を説明してくださり、質問にも素早く答えてくれたので安心してお任せできました。作業も迅速で、思っていたよりスムーズに完了。こちらの要望もしっかり聞いてくれて、サービスの質に大変満足しています。また何かあれば間違いなくリピートしたいと思える良いサービスでした。</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
@@ -35393,17 +35305,17 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
+          <t>https://fuyouhincenter.jp/ecosuketto/</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/ecosuketto.png</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡の評判・口コミ</t>
+          <t>ECO助っ人の評判・口コミ</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
@@ -35413,42 +35325,42 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
         <is>
-          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
+          <t>最短即日で作業を依頼できる / 全国各地でサービスを利用できる / 業界最安値に挑戦中</t>
         </is>
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
+          <t>不用品1点から大量の不用品まで回収してもらえます。 全国各地でサービスを提供していて、年間20,000件の実績があります。 見積もりや基本料金は無料で、24時間いつでも予約可能です。</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
         <is>
-          <t>https://koyorecycle.com/</t>
+          <t>https://eco-suketto.jp/</t>
         </is>
       </c>
     </row>
@@ -35461,72 +35373,72 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>company-6234</t>
+          <t>company-380</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>便利屋お助けマスター</t>
+          <t>紅葉リサイクル福岡</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>3.87 （ 4 件 ）</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>4.42 （ 7 件 ）</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
+          <t>少量プラン：5,000円～ / 軽トラック積み放題：8,000円～ / 1トントラック積み放題 ：15,000円～ / 2トントラック積み放題：20,000円～ / 1.5トンアルミバン積み放題：40,000円～</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの最新の口コミ</t>
+          <t>紅葉リサイクル福岡の最新の口コミ</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>40代 男性</t>
+          <t>63歳・女性</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -35536,77 +35448,77 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度4・対応5）</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
+          <t>メール見積もりのあと、紅葉リサイクルに3階建ての部屋から大型家具を回収してもらいました。パパッと運んでくれて助かりました。1.5トンのトラックには入る物量だと思っていましたが、実際は超えていたみたいです。でも紅葉リサイクルのおかげで1.5tの料金だけで済みました。本当にありがとうございます。ただ、次回は現地見積もりを頼もうと思います。メールだけだと把握し切れないこともあるので、トラブル防止のためにも現地確認は重要だと感じました。紅葉リサイクルにはこれからも頼みたいと思います。</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/otasuke-master/</t>
+          <t>https://fuyouhincenter.jp/kouyourecyclefukuoka/</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/kouyourecyclefukuoka.png</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>便利屋お助けマスターの評判・口コミ</t>
+          <t>紅葉リサイクル福岡の評判・口コミ</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
         <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>7件</t>
-        </is>
-      </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
         <is>
-          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
+          <t>他社より1円でも高ければ必ず値引き / 日新火災海上保険に加入しており、最大1000万円の補償あり / 1点から不用品を回収してもらえる</t>
         </is>
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
+          <t>紅葉リサイクル福岡は、福岡限定でサービスを提供する不用品回収業者です。 見積り料金からの追加料金は一切なく、安心して依頼することが出来ます。 また、遺品整理士認定協会の優良企業となっています。</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
         <is>
-          <t>https://otasuke-master.co.jp/</t>
+          <t>https://koyorecycle.com/</t>
         </is>
       </c>
     </row>
@@ -35619,72 +35531,72 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>company-8102</t>
+          <t>company-6234</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>片付け堂</t>
+          <t>便利屋お助けマスター</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>5 （ 2 件 ）</t>
+          <t>4.42 （ 7 件 ）</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
+          <t>北海道 / 岩手県 / 秋田県 / 宮城県 / 青森県 / 山形県 / 福島県 / 東京都 / 埼玉県 / 茨城県 / 栃木県 / 群馬県 / 神奈川県 / 千葉県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 大阪府 / 滋賀県 / 京都府 / 兵庫県 / 奈良県 / 和歌山県 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 高知県 / 徳島県 / 熊本県 / 宮崎県 / 佐賀県 / 福岡県 / 鹿児島県 / 沖縄県 / 大分県 / 長崎県</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
+          <t>車両費：1台3,300円〜 / 作業費：1名3,300円〜（1時間） / 出張費：1名2,200円</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>片付け堂の最新の口コミ</t>
+          <t>便利屋お助けマスターの最新の口コミ</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>40代 男性</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -35699,47 +35611,47 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
+          <t>祖父母の家を片付けるためにお願いしました。部屋数が多く不安でしたが、スタッフの方々がチームで見事に連携しながら作業していて、手際の良さにびっくり。中には階段での運搬が必要な大型家具もありましたが、追加料金もなく気持ちよく引き受けてくれました。</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/katazukedou/</t>
+          <t>https://fuyouhincenter.jp/otasuke-master/</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/10/benriyamaster.png</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>片付け堂の評判・口コミ</t>
+          <t>便利屋お助けマスターの評判・口コミ</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
@@ -35749,22 +35661,22 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
         <is>
-          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
+          <t>47都道府県全てで対応しているため、場所を問わず依頼が可能 / 追加料金が一切ないため、見積もり後に予期しない料金が発生しない / 不用品回収から草刈り、引っ越しサポート、DIYまで多彩な依頼に対応</t>
         </is>
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
+          <t>【全国対応】便利屋お助けマスターでお困りごとは何でも解決！は、全国対応の便利屋サービスで、365日年中無休で不用品回収を含む多様な依頼に対応しています。 最短30分で駆けつけ、追加料金なしの明朗会計が特徴です。 また、迅速で柔軟なサービスが強みです。 奈良の便利屋お助けマスターで何でも解決！の奈良本店もあります。</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>https://www.katazukedou.com/</t>
+          <t>https://otasuke-master.co.jp/</t>
         </is>
       </c>
     </row>
@@ -35777,27 +35689,27 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>company-3871</t>
+          <t>company-8102</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>福島片付け110番</t>
+          <t>片付け堂</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -35807,42 +35719,42 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>5 （ 3 件 ）</t>
+          <t>5 （ 2 件 ）</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>女性スタッフ在籍 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>北海道 / 青森県 / 福島県 / 東京都 / 埼玉県 / 栃木県 / 群馬県 / 神奈川県 / 富山県 / 大阪府 / 京都府 / 岡山県 / 広島県 / 島根県 / 鳥取県 / 山口県 / 香川県 / 愛媛県 / 宮崎県</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
+          <t>軽トラ：19,800円～ / 2tトラック：33,000円～ / 4tトラック：61,600円～</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>福島片付け110番の最新の口コミ</t>
+          <t>片付け堂の最新の口コミ</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>40代・男性</t>
+          <t>60代・女性</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -35852,32 +35764,32 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度5・対応5）</t>
+          <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
+          <t>エレベータのない4階からの運び出しもしてくれました。自分では対応出来なかったので、非常に助かりました。ありがとうございました。</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
+          <t>https://fuyouhincenter.jp/katazukedou/</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/11/katadukedou.png</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>福島片付け110番の評判・口コミ</t>
+          <t>片付け堂の評判・口コミ</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
@@ -35892,17 +35804,17 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
@@ -35912,17 +35824,17 @@
       </c>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
+          <t>作業実績は累計20,000件以上で実績あり / 料金体系が明瞭でクレジットカード決済など支払方法も充実 / 全加盟店が一般廃棄物収集運搬業の許認可を取得</t>
         </is>
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
+          <t>片付け堂は、北海道から九州まで展開する全国チェーンの不用品回収・粗大ごみ回収業者です。全加盟店が一般廃棄物収集運搬業の許認可を取得し、作業実績は累計20,000件以上。料金は軽トラック1台分19,800円（税込）から明瞭な料金体系で、見積り無料、事前下見も可能です。年中無休で受付時間は8:30～17:30、クレジットカード決済に対応し、Tポイントも貯まります。※エリアによってTポイントに対応していない場合があります。</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
         <is>
-          <t>https://fukushima-kataduke110ban.com/</t>
+          <t>https://www.katazukedou.com/</t>
         </is>
       </c>
     </row>
@@ -35935,87 +35847,87 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>company-3850</t>
+          <t>company-3871</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>フロンティアグループ</t>
+          <t>福島片付け110番</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>4.5 （ 4 件 ）</t>
+          <t>5 （ 3 件 ）</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 立ち合い不要で回収作業可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>福島県 / 茨城県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
+          <t>少量回収プラン： / 軽トラックに積み放題！プラン：25,000円～ / 2トントラックに積み放題！プラン：60,000円～ / 4トントラックに積み放題！プラン：120,000円～</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>フロンティアグループの最新の口コミ</t>
+          <t>福島片付け110番の最新の口コミ</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>30歳・男性</t>
+          <t>40代・男性</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>（回収料金4・回収速度4・対応4）</t>
+          <t>（回収料金4・回収速度5・対応5）</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
+          <t>遺品整理でどこに相談したら良いか分からなくて困っていました。分別も丁寧にやってくださり、とても良心的でよかったです。</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
@@ -36025,62 +35937,62 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
+          <t>https://fuyouhincenter.jp/fukushima-kataduke110ban/</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/fukushima-kataduke110ban.png</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>フロンティアグループの評判・口コミ</t>
+          <t>福島片付け110番の評判・口コミ</t>
         </is>
       </c>
       <c r="X232" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
         <is>
-          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
+          <t>立ち合い不要で、忙しい方にも便利 / 幅広いサービス対応で、あらゆる片付けニーズに応えられる / 365日24時間対応で、急な依頼にも即対応可能</t>
         </is>
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
+          <t>福島県全域で不用品回収や遺品整理、ゴミ屋敷整理を24時間365日対応しています。 迅速な対応と明瞭会計を特徴とし、賠償責任保険を完備しているため、安心して依頼できます。 高価買取や立ち合い不要のサービスも提供し、あらゆる片付けニーズに対応する柔軟なサービスが魅力です。</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
         <is>
-          <t>https://iwaki-benriya.com/</t>
+          <t>https://fukushima-kataduke110ban.com/</t>
         </is>
       </c>
     </row>
@@ -36093,27 +36005,27 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>company-615</t>
+          <t>company-3850</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>フロンティアグループ</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>エコスピード</t>
+          <t>フロンティアグループ</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -36123,7 +36035,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>4.75 （ 4 件 ）</t>
+          <t>4.5 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -36133,67 +36045,67 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / 買取対応 / 単品回収可能 / 無料の出張見積り有り</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
+          <t>福島県 / 茨城県</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
+          <t>少量1個～の個別料金プラン： / お部屋まるごと定額プラン： / 人気の積み放題定額プラン：</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>エコスピードの最新の口コミ</t>
+          <t>フロンティアグループの最新の口コミ</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>30代 女性</t>
+          <t>30歳・男性</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>（回収料金5・回収速度5・対応5）</t>
+          <t>（回収料金4・回収速度4・対応4）</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
+          <t>口コミの評判を見て初めて依頼しましたが、期待通りの素晴らしいサービスでした。問い合わせへの返信が早く、見積もり金額から追加料金なしで完了してくれたので安心感がありました。特に印象的だったのは、研修中の新しいスタッフと指導する上司の姿勢です。若手社員が一生懸命作業する様子と、それをサポートする上司の丁寧な指導が見られ、会社の雰囲気の良さが伝わってきました。次回も迷わずお願いしたいと思います！</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon02.png</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/ecospeed/</t>
+          <t>https://fuyouhincenter.jp/iwaki-benriya/</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/iwaki-benriya.png</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>エコスピードの評判・口コミ</t>
+          <t>フロンティアグループの評判・口コミ</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
@@ -36203,7 +36115,7 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
@@ -36213,32 +36125,32 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
         <is>
-          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
+          <t>即日対応可能で、緊急の不用品回収にも対応 / 幅広い対応エリアで、地域を問わず利用可能 / リサイクルや買取にも対応し、費用を抑えられる</t>
         </is>
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
+          <t>福島県と茨城県を中心に不用品回収、買取、廃品回収を提供しています。 福島の不用品回収実績がNo.1で、明確な料金プランと顧客満足度の高さが特徴です。 また、即日対応や年中無休のサービスを提供し、引っ越しや遺品整理など幅広いニーズに対応しています。</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
         <is>
-          <t>https://eco-speed.life/</t>
+          <t>https://iwaki-benriya.com/</t>
         </is>
       </c>
     </row>
@@ -36251,72 +36163,72 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>company-3839</t>
+          <t>company-615</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>エコスピード</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島</t>
+          <t>エコスピード</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>5 （ 1 件 ）</t>
+          <t>4.75 （ 4 件 ）</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+          <t>深夜・早朝の回収 / 即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>東京都 / 埼玉県 / 千葉県 / 静岡県</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+          <t>軽トラック詰め放題パック：9,800円（税別）～ / 1tトラック詰め放題パック：24,800円（税別）～ / 2tトラック詰め放題パック：49,800円（税別）～</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の最新の口コミ</t>
+          <t>エコスピードの最新の口コミ</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>60代・女性</t>
+          <t>30代 女性</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -36331,7 +36243,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+          <t>物をなかなか捨てられない性格で、家の中が不用品だらけになってしまっていました。エコスピードさんは訪問時から親身になって相談に乗ってくれ、寄り添ってくれたのが印象的でした。片付けを終えた後のスッキリ感がすごいです。</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
@@ -36341,62 +36253,62 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+          <t>https://fuyouhincenter.jp/ecospeed/</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/05/スクリーンショット-2024-05-15-131749.png</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>不用品回収セブン福島の評判・口コミ</t>
+          <t>エコスピードの評判・口コミ</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
         <is>
-          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+          <t>最短30分で現地に到着できる / 年中無休で深夜も対応してくれる / 「不用品回収の窓口」優良加盟店</t>
         </is>
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+          <t>エコスピードは、関東・静岡を中心に不用品回収のサービスを提供しています。 年中無休で、最短30分で到着可能と対応スピードの速さが特徴です。</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
         <is>
-          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+          <t>https://eco-speed.life/</t>
         </is>
       </c>
     </row>
@@ -36409,150 +36321,308 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
+          <t>company-3839</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>5 （ 1 件 ）</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>即日対応 / 遺品整理/ゴミ屋敷清掃の対応可 / クレジットカード払い対応 / 買取対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>ミニパック（小）：5,500円（税込）～ / ミニパック（大）：11,000円（税込）～ / レギュラーパック：16,500円（税込）～ / ファミリーパック(小)：33,000円（税込）〜 / ファミリーパック(大)：55,000円（税込）〜</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の最新の口コミ</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>60代・女性</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>（回収料金5・回収速度5・対応5）</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>引っ越しの際に利用させていただきました。冷蔵庫、洗濯機等、重い家電の処分が楽にできたのがありがたかったです。最初に予定していたよりも不用品が多くなってしまっていたのですが、想像していたよりも安く済みました。</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/seven-fukushima/</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>https://fuyouhincenter.jp/wp-content/uploads/2024/08/seven-fukushima.png</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>不用品回収セブン福島の評判・口コミ</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>遺品整理士が在籍しており、遺品整理にも対応 / 最短即日対応で、急な依頼にも対応可能 / 24時間365日対応で、いつでも相談可能</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>福島県全域で迅速かつ信頼性の高い不用品回収サービスを提供しています。 家庭や法人の不用品整理、遺品整理、生前整理に対応し、リサイクルや再利用も考慮した環境に優しい処理を行います。 さらに、24時間365日対応で、急な依頼にも柔軟に対応します。</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>https://www.huyouhinkaisyuu-fukushima.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>16</v>
+      </c>
+      <c r="B236" t="n">
+        <v>10</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
           <t>company-418</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F236" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G236" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
         <is>
           <t>5 （ 2 件 ）</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
+      <c r="J236" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="K236" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="L236" t="inlineStr">
         <is>
           <t>深夜・早朝の回収 / 即日対応 / クレジットカード払い対応 / 単品回収可能 / 無料の出張見積り有り / エアコンの取り外し可</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t>福岡県 / 長崎県</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
+      <c r="N236" t="inlineStr">
         <is>
           <t>単品回収：1点1,000円より</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr">
+      <c r="O236" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の最新の口コミ</t>
         </is>
       </c>
-      <c r="P235" t="inlineStr">
+      <c r="P236" t="inlineStr">
         <is>
           <t>59歳・女性</t>
         </is>
       </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R235" t="inlineStr">
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
         <is>
           <t>（回収料金5・回収速度5・対応5）</t>
         </is>
       </c>
-      <c r="S235" t="inlineStr">
+      <c r="S236" t="inlineStr">
         <is>
           <t>問い合わせの迅速な対応。当日も親切に対応していただきました。また機会があれば利用したいと思います。ありがとうございました。</t>
         </is>
       </c>
-      <c r="T235" t="inlineStr">
+      <c r="T236" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2023/12/reviews_icon01.png</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="U236" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/ritouhikkoshirescue/</t>
         </is>
       </c>
-      <c r="V235" t="inlineStr">
+      <c r="V236" t="inlineStr">
         <is>
           <t>https://fuyouhincenter.jp/wp-content/uploads/2024/03/ritouhikkoshirescue.jpeg-samune.png</t>
         </is>
       </c>
-      <c r="W235" t="inlineStr">
+      <c r="W236" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊の評判・口コミ</t>
         </is>
       </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
         <is>
           <t>2件</t>
         </is>
       </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
         <is>
           <t>1点から不用品を回収してもらえる / 引越しとセットで依頼するとお得 / LINEでスピード見積もりに対応</t>
         </is>
       </c>
-      <c r="AE235" t="inlineStr">
+      <c r="AE236" t="inlineStr">
         <is>
           <t>離島引越しレスキュー隊はお得な引越し+不用品回収プランを提供しています。 お問い合わせから最短即日で対応してもらえます。 また、一般廃棄物収集運搬業許可を取得する優良企業です。</t>
         </is>
       </c>
-      <c r="AF235" t="inlineStr"/>
+      <c r="AF236" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/fuyouhincenter_wastecollection_comp.xlsx
+++ b/scripts/fuyouhincenter_wastecollection_comp.xlsx
@@ -14207,12 +14207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5 （ 2 件の口コミ・評判 ）</t>
+          <t>5 （ 3 件の口コミ・評判 ）</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
